--- a/MEDIBELL_3SHEETS.xlsx
+++ b/MEDIBELL_3SHEETS.xlsx
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0.83</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0.95</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0.83</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45722</v>
       </c>
       <c r="F2" t="n">
-        <v>45722.54166666666</v>
+        <v>45722.5416666667</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>400</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>45725.54166666666</v>
+        <v>45725.5416666667</v>
       </c>
     </row>
     <row r="3">
@@ -14940,7 +14940,7 @@
         <v>45727</v>
       </c>
       <c r="F3" t="n">
-        <v>45727.58333333334</v>
+        <v>45727.5833333333</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>400</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>45736.58333333334</v>
+        <v>45736.5833333333</v>
       </c>
     </row>
     <row r="4">
@@ -15090,7 +15090,7 @@
         <v>45695</v>
       </c>
       <c r="F5" t="n">
-        <v>45695.79166666666</v>
+        <v>45695.7916666667</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -15116,7 +15116,7 @@
         <v>400</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>45700.79166666666</v>
+        <v>45700.7916666667</v>
       </c>
     </row>
     <row r="6">
@@ -15165,7 +15165,7 @@
         <v>45710</v>
       </c>
       <c r="F6" t="n">
-        <v>45710.54166666666</v>
+        <v>45710.5416666667</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>400</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>45721.54166666666</v>
+        <v>45721.5416666667</v>
       </c>
     </row>
     <row r="7">
@@ -15240,7 +15240,7 @@
         <v>45711</v>
       </c>
       <c r="F7" t="n">
-        <v>45711.79166666666</v>
+        <v>45711.7916666667</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>45730.79166666666</v>
+        <v>45730.7916666667</v>
       </c>
     </row>
     <row r="8">
@@ -15315,7 +15315,7 @@
         <v>45727</v>
       </c>
       <c r="F8" t="n">
-        <v>45727.83333333334</v>
+        <v>45727.8333333333</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>45736.83333333334</v>
+        <v>45736.8333333333</v>
       </c>
     </row>
     <row r="9">
@@ -15390,7 +15390,7 @@
         <v>45713</v>
       </c>
       <c r="F9" t="n">
-        <v>45713.79166666666</v>
+        <v>45713.7916666667</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>650</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>45724.79166666666</v>
+        <v>45724.7916666667</v>
       </c>
     </row>
     <row r="10">
@@ -15540,7 +15540,7 @@
         <v>45693</v>
       </c>
       <c r="F11" t="n">
-        <v>45693.41666666666</v>
+        <v>45693.4166666667</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>500</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>45712.41666666666</v>
+        <v>45712.4166666667</v>
       </c>
     </row>
     <row r="12">
@@ -15690,7 +15690,7 @@
         <v>45694</v>
       </c>
       <c r="F13" t="n">
-        <v>45694.45833333334</v>
+        <v>45694.4583333333</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>45702.45833333334</v>
+        <v>45702.4583333333</v>
       </c>
     </row>
     <row r="14">
@@ -15765,7 +15765,7 @@
         <v>45708</v>
       </c>
       <c r="F14" t="n">
-        <v>45708.45833333334</v>
+        <v>45708.4583333333</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>500</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>45723.45833333334</v>
+        <v>45723.4583333333</v>
       </c>
     </row>
     <row r="15">
@@ -15915,7 +15915,7 @@
         <v>45697</v>
       </c>
       <c r="F16" t="n">
-        <v>45697.58333333334</v>
+        <v>45697.5833333333</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>650</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>45710.58333333334</v>
+        <v>45710.5833333333</v>
       </c>
     </row>
     <row r="17">
@@ -15990,7 +15990,7 @@
         <v>45723</v>
       </c>
       <c r="F17" t="n">
-        <v>45723.54166666666</v>
+        <v>45723.5416666667</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>250</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>45735.54166666666</v>
+        <v>45735.5416666667</v>
       </c>
     </row>
     <row r="18">
@@ -16140,7 +16140,7 @@
         <v>45710</v>
       </c>
       <c r="F19" t="n">
-        <v>45710.41666666666</v>
+        <v>45710.4166666667</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>250</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>45722.41666666666</v>
+        <v>45722.4166666667</v>
       </c>
     </row>
     <row r="20">
@@ -16290,7 +16290,7 @@
         <v>45693</v>
       </c>
       <c r="F21" t="n">
-        <v>45693.45833333334</v>
+        <v>45693.4583333333</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>500</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>45705.45833333334</v>
+        <v>45705.4583333333</v>
       </c>
     </row>
     <row r="22">
@@ -16515,7 +16515,7 @@
         <v>45691</v>
       </c>
       <c r="F24" t="n">
-        <v>45691.79166666666</v>
+        <v>45691.7916666667</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>10</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>45696.79166666666</v>
+        <v>45696.7916666667</v>
       </c>
     </row>
     <row r="25">
@@ -16590,7 +16590,7 @@
         <v>45706</v>
       </c>
       <c r="F25" t="n">
-        <v>45706.41666666666</v>
+        <v>45706.4166666667</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>500</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>45717.41666666666</v>
+        <v>45717.4166666667</v>
       </c>
     </row>
     <row r="26">
@@ -16665,7 +16665,7 @@
         <v>45726</v>
       </c>
       <c r="F26" t="n">
-        <v>45726.54166666666</v>
+        <v>45726.5416666667</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>1000</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>45745.54166666666</v>
+        <v>45745.5416666667</v>
       </c>
     </row>
     <row r="27">
@@ -16965,7 +16965,7 @@
         <v>45696</v>
       </c>
       <c r="F30" t="n">
-        <v>45696.54166666666</v>
+        <v>45696.5416666667</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>10</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>45704.54166666666</v>
+        <v>45704.5416666667</v>
       </c>
     </row>
     <row r="31">
@@ -17115,7 +17115,7 @@
         <v>45700</v>
       </c>
       <c r="F32" t="n">
-        <v>45700.79166666666</v>
+        <v>45700.7916666667</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>1000</v>
       </c>
       <c r="L32" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>45703.79166666666</v>
+        <v>45703.7916666667</v>
       </c>
     </row>
     <row r="33">
@@ -17265,7 +17265,7 @@
         <v>45700</v>
       </c>
       <c r="F34" t="n">
-        <v>45700.79166666666</v>
+        <v>45700.7916666667</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>10</v>
       </c>
       <c r="L34" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>45703.79166666666</v>
+        <v>45703.7916666667</v>
       </c>
     </row>
     <row r="35">
@@ -17490,7 +17490,7 @@
         <v>45728</v>
       </c>
       <c r="F37" t="n">
-        <v>45728.41666666666</v>
+        <v>45728.4166666667</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -17516,7 +17516,7 @@
         <v>1000</v>
       </c>
       <c r="L37" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>45744.41666666666</v>
+        <v>45744.4166666667</v>
       </c>
     </row>
     <row r="38">
@@ -17565,7 +17565,7 @@
         <v>45726</v>
       </c>
       <c r="F38" t="n">
-        <v>45726.66666666666</v>
+        <v>45726.6666666667</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>10</v>
       </c>
       <c r="L38" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>45732.66666666666</v>
+        <v>45732.6666666667</v>
       </c>
     </row>
     <row r="39">
@@ -17640,7 +17640,7 @@
         <v>45722</v>
       </c>
       <c r="F39" t="n">
-        <v>45722.79166666666</v>
+        <v>45722.7916666667</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>250</v>
       </c>
       <c r="L39" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>45727.79166666666</v>
+        <v>45727.7916666667</v>
       </c>
     </row>
     <row r="40">
@@ -17715,7 +17715,7 @@
         <v>45723</v>
       </c>
       <c r="F40" t="n">
-        <v>45723.66666666666</v>
+        <v>45723.6666666667</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>650</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>45727.66666666666</v>
+        <v>45727.6666666667</v>
       </c>
     </row>
     <row r="41">
@@ -17865,7 +17865,7 @@
         <v>45694</v>
       </c>
       <c r="F42" t="n">
-        <v>45694.58333333334</v>
+        <v>45694.5833333333</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>400</v>
       </c>
       <c r="L42" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>45709.58333333334</v>
+        <v>45709.5833333333</v>
       </c>
     </row>
     <row r="43">
@@ -18015,7 +18015,7 @@
         <v>45711</v>
       </c>
       <c r="F44" t="n">
-        <v>45711.83333333334</v>
+        <v>45711.8333333333</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>250</v>
       </c>
       <c r="L44" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>45730.83333333334</v>
+        <v>45730.8333333333</v>
       </c>
     </row>
     <row r="45">
@@ -18090,7 +18090,7 @@
         <v>45696</v>
       </c>
       <c r="F45" t="n">
-        <v>45696.79166666666</v>
+        <v>45696.7916666667</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>500</v>
       </c>
       <c r="L45" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>45713.79166666666</v>
+        <v>45713.7916666667</v>
       </c>
     </row>
     <row r="46">
@@ -18240,7 +18240,7 @@
         <v>45705</v>
       </c>
       <c r="F47" t="n">
-        <v>45705.83333333334</v>
+        <v>45705.8333333333</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>1000</v>
       </c>
       <c r="L47" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>45712.83333333334</v>
+        <v>45712.8333333333</v>
       </c>
     </row>
     <row r="48">
@@ -18315,7 +18315,7 @@
         <v>45724</v>
       </c>
       <c r="F48" t="n">
-        <v>45724.83333333334</v>
+        <v>45724.8333333333</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>650</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>45737.83333333334</v>
+        <v>45737.8333333333</v>
       </c>
     </row>
     <row r="49">
@@ -18465,7 +18465,7 @@
         <v>45715</v>
       </c>
       <c r="F50" t="n">
-        <v>45715.66666666666</v>
+        <v>45715.6666666667</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>650</v>
       </c>
       <c r="L50" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>45732.66666666666</v>
+        <v>45732.6666666667</v>
       </c>
     </row>
     <row r="51">
@@ -18690,7 +18690,7 @@
         <v>45691</v>
       </c>
       <c r="F53" t="n">
-        <v>45691.70833333334</v>
+        <v>45691.7083333333</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>500</v>
       </c>
       <c r="L53" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>45702.70833333334</v>
+        <v>45702.7083333333</v>
       </c>
     </row>
     <row r="54">
@@ -18765,7 +18765,7 @@
         <v>45700</v>
       </c>
       <c r="F54" t="n">
-        <v>45700.66666666666</v>
+        <v>45700.6666666667</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -18791,7 +18791,7 @@
         <v>650</v>
       </c>
       <c r="L54" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>45710.66666666666</v>
+        <v>45710.6666666667</v>
       </c>
     </row>
     <row r="55">
@@ -18840,7 +18840,7 @@
         <v>45703</v>
       </c>
       <c r="F55" t="n">
-        <v>45703.45833333334</v>
+        <v>45703.4583333333</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>10</v>
       </c>
       <c r="L55" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>45706.45833333334</v>
+        <v>45706.4583333333</v>
       </c>
     </row>
     <row r="56">
@@ -18915,7 +18915,7 @@
         <v>45720</v>
       </c>
       <c r="F56" t="n">
-        <v>45720.83333333334</v>
+        <v>45720.8333333333</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>400</v>
       </c>
       <c r="L56" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>45731.83333333334</v>
+        <v>45731.8333333333</v>
       </c>
     </row>
     <row r="57">
@@ -18990,7 +18990,7 @@
         <v>45703</v>
       </c>
       <c r="F57" t="n">
-        <v>45703.41666666666</v>
+        <v>45703.4166666667</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>250</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>45716.41666666666</v>
+        <v>45716.4166666667</v>
       </c>
     </row>
     <row r="58">
@@ -19065,7 +19065,7 @@
         <v>45710</v>
       </c>
       <c r="F58" t="n">
-        <v>45710.66666666666</v>
+        <v>45710.6666666667</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>250</v>
       </c>
       <c r="L58" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>45717.66666666666</v>
+        <v>45717.6666666667</v>
       </c>
     </row>
     <row r="59">
@@ -19140,7 +19140,7 @@
         <v>45702</v>
       </c>
       <c r="F59" t="n">
-        <v>45702.79166666666</v>
+        <v>45702.7916666667</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>400</v>
       </c>
       <c r="L59" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>45721.79166666666</v>
+        <v>45721.7916666667</v>
       </c>
     </row>
     <row r="60">
@@ -19215,7 +19215,7 @@
         <v>45705</v>
       </c>
       <c r="F60" t="n">
-        <v>45705.45833333334</v>
+        <v>45705.4583333333</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>500</v>
       </c>
       <c r="L60" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>45709.45833333334</v>
+        <v>45709.4583333333</v>
       </c>
     </row>
     <row r="61">
@@ -19290,7 +19290,7 @@
         <v>45712</v>
       </c>
       <c r="F61" t="n">
-        <v>45712.66666666666</v>
+        <v>45712.6666666667</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>1000</v>
       </c>
       <c r="L61" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>45718.66666666666</v>
+        <v>45718.6666666667</v>
       </c>
     </row>
     <row r="62">
@@ -19365,7 +19365,7 @@
         <v>45719</v>
       </c>
       <c r="F62" t="n">
-        <v>45719.66666666666</v>
+        <v>45719.6666666667</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>400</v>
       </c>
       <c r="L62" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>45732.66666666666</v>
+        <v>45732.6666666667</v>
       </c>
     </row>
     <row r="63">
@@ -19515,7 +19515,7 @@
         <v>45717</v>
       </c>
       <c r="F64" t="n">
-        <v>45717.70833333334</v>
+        <v>45717.7083333333</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>650</v>
       </c>
       <c r="L64" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>45724.70833333334</v>
+        <v>45724.7083333333</v>
       </c>
     </row>
     <row r="65">
@@ -19965,7 +19965,7 @@
         <v>45690</v>
       </c>
       <c r="F70" t="n">
-        <v>45690.45833333334</v>
+        <v>45690.4583333333</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>500</v>
       </c>
       <c r="L70" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>45695.45833333334</v>
+        <v>45695.4583333333</v>
       </c>
     </row>
     <row r="71">
@@ -20040,7 +20040,7 @@
         <v>45705</v>
       </c>
       <c r="F71" t="n">
-        <v>45705.41666666666</v>
+        <v>45705.4166666667</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>500</v>
       </c>
       <c r="L71" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>45714.41666666666</v>
+        <v>45714.4166666667</v>
       </c>
     </row>
     <row r="72">
@@ -20115,7 +20115,7 @@
         <v>45698</v>
       </c>
       <c r="F72" t="n">
-        <v>45698.83333333334</v>
+        <v>45698.8333333333</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>650</v>
       </c>
       <c r="L72" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>45708.83333333334</v>
+        <v>45708.8333333333</v>
       </c>
     </row>
     <row r="73">
@@ -20190,7 +20190,7 @@
         <v>45690</v>
       </c>
       <c r="F73" t="n">
-        <v>45690.54166666666</v>
+        <v>45690.5416666667</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>250</v>
       </c>
       <c r="L73" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>45709.54166666666</v>
+        <v>45709.5416666667</v>
       </c>
     </row>
     <row r="74">
@@ -20340,7 +20340,7 @@
         <v>45694</v>
       </c>
       <c r="F75" t="n">
-        <v>45694.41666666666</v>
+        <v>45694.4166666667</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>500</v>
       </c>
       <c r="L75" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>45708.41666666666</v>
+        <v>45708.4166666667</v>
       </c>
     </row>
     <row r="76">
@@ -20415,7 +20415,7 @@
         <v>45722</v>
       </c>
       <c r="F76" t="n">
-        <v>45722.83333333334</v>
+        <v>45722.8333333333</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>650</v>
       </c>
       <c r="L76" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>45732.83333333334</v>
+        <v>45732.8333333333</v>
       </c>
     </row>
     <row r="77">
@@ -20640,7 +20640,7 @@
         <v>45715</v>
       </c>
       <c r="F79" t="n">
-        <v>45715.83333333334</v>
+        <v>45715.8333333333</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>500</v>
       </c>
       <c r="L79" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>45735.83333333334</v>
+        <v>45735.8333333333</v>
       </c>
     </row>
     <row r="80">
@@ -20790,7 +20790,7 @@
         <v>45698</v>
       </c>
       <c r="F81" t="n">
-        <v>45698.79166666666</v>
+        <v>45698.7916666667</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>10</v>
       </c>
       <c r="L81" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>45702.79166666666</v>
+        <v>45702.7916666667</v>
       </c>
     </row>
     <row r="82">
@@ -20865,7 +20865,7 @@
         <v>45704</v>
       </c>
       <c r="F82" t="n">
-        <v>45704.41666666666</v>
+        <v>45704.4166666667</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>400</v>
       </c>
       <c r="L82" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>45723.41666666666</v>
+        <v>45723.4166666667</v>
       </c>
     </row>
     <row r="83">
@@ -20940,7 +20940,7 @@
         <v>45698</v>
       </c>
       <c r="F83" t="n">
-        <v>45698.66666666666</v>
+        <v>45698.6666666667</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
         <v>1000</v>
       </c>
       <c r="L83" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>45712.66666666666</v>
+        <v>45712.6666666667</v>
       </c>
     </row>
     <row r="84">
@@ -21015,7 +21015,7 @@
         <v>45706</v>
       </c>
       <c r="F84" t="n">
-        <v>45706.54166666666</v>
+        <v>45706.5416666667</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>250</v>
       </c>
       <c r="L84" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>45711.54166666666</v>
+        <v>45711.5416666667</v>
       </c>
     </row>
     <row r="85">
@@ -21240,7 +21240,7 @@
         <v>45720</v>
       </c>
       <c r="F87" t="n">
-        <v>45720.58333333334</v>
+        <v>45720.5833333333</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>250</v>
       </c>
       <c r="L87" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>45733.58333333334</v>
+        <v>45733.5833333333</v>
       </c>
     </row>
     <row r="88">
@@ -21315,7 +21315,7 @@
         <v>45692</v>
       </c>
       <c r="F88" t="n">
-        <v>45692.41666666666</v>
+        <v>45692.4166666667</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>10</v>
       </c>
       <c r="L88" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>45706.41666666666</v>
+        <v>45706.4166666667</v>
       </c>
     </row>
     <row r="89">
@@ -21465,7 +21465,7 @@
         <v>45708</v>
       </c>
       <c r="F90" t="n">
-        <v>45708.79166666666</v>
+        <v>45708.7916666667</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>500</v>
       </c>
       <c r="L90" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>45716.79166666666</v>
+        <v>45716.7916666667</v>
       </c>
     </row>
     <row r="91">
@@ -21540,7 +21540,7 @@
         <v>45689</v>
       </c>
       <c r="F91" t="n">
-        <v>45689.58333333334</v>
+        <v>45689.5833333333</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>1000</v>
       </c>
       <c r="L91" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>45698.58333333334</v>
+        <v>45698.5833333333</v>
       </c>
     </row>
     <row r="92">
@@ -21615,7 +21615,7 @@
         <v>45707</v>
       </c>
       <c r="F92" t="n">
-        <v>45707.41666666666</v>
+        <v>45707.4166666667</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>400</v>
       </c>
       <c r="L92" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>45725.41666666666</v>
+        <v>45725.4166666667</v>
       </c>
     </row>
     <row r="93">
@@ -21690,7 +21690,7 @@
         <v>45709</v>
       </c>
       <c r="F93" t="n">
-        <v>45709.70833333334</v>
+        <v>45709.7083333333</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>650</v>
       </c>
       <c r="L93" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>45720.70833333334</v>
+        <v>45720.7083333333</v>
       </c>
     </row>
     <row r="94">
@@ -21765,7 +21765,7 @@
         <v>45728</v>
       </c>
       <c r="F94" t="n">
-        <v>45728.83333333334</v>
+        <v>45728.8333333333</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>500</v>
       </c>
       <c r="L94" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>45731.83333333334</v>
+        <v>45731.8333333333</v>
       </c>
     </row>
     <row r="95">
@@ -21840,7 +21840,7 @@
         <v>45728</v>
       </c>
       <c r="F95" t="n">
-        <v>45728.79166666666</v>
+        <v>45728.7916666667</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>400</v>
       </c>
       <c r="L95" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>45734.79166666666</v>
+        <v>45734.7916666667</v>
       </c>
     </row>
     <row r="96">
@@ -21990,7 +21990,7 @@
         <v>45706</v>
       </c>
       <c r="F97" t="n">
-        <v>45706.41666666666</v>
+        <v>45706.4166666667</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>500</v>
       </c>
       <c r="L97" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>45720.41666666666</v>
+        <v>45720.4166666667</v>
       </c>
     </row>
     <row r="98">
@@ -22140,7 +22140,7 @@
         <v>45704</v>
       </c>
       <c r="F99" t="n">
-        <v>45704.66666666666</v>
+        <v>45704.6666666667</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>650</v>
       </c>
       <c r="L99" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>45717.66666666666</v>
+        <v>45717.6666666667</v>
       </c>
     </row>
     <row r="100">
@@ -22290,7 +22290,7 @@
         <v>45693</v>
       </c>
       <c r="F101" t="n">
-        <v>45693.66666666666</v>
+        <v>45693.6666666667</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>500</v>
       </c>
       <c r="L101" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>45713.66666666666</v>
+        <v>45713.6666666667</v>
       </c>
     </row>
     <row r="102">
@@ -22515,7 +22515,7 @@
         <v>45728</v>
       </c>
       <c r="F104" t="n">
-        <v>45728.45833333334</v>
+        <v>45728.4583333333</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>250</v>
       </c>
       <c r="L104" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>45747.45833333334</v>
+        <v>45747.4583333333</v>
       </c>
     </row>
     <row r="105">
@@ -22590,7 +22590,7 @@
         <v>45697</v>
       </c>
       <c r="F105" t="n">
-        <v>45697.58333333334</v>
+        <v>45697.5833333333</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>500</v>
       </c>
       <c r="L105" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>45712.58333333334</v>
+        <v>45712.5833333333</v>
       </c>
     </row>
     <row r="106">
@@ -22665,7 +22665,7 @@
         <v>45711</v>
       </c>
       <c r="F106" t="n">
-        <v>45711.66666666666</v>
+        <v>45711.6666666667</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>500</v>
       </c>
       <c r="L106" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>45727.66666666666</v>
+        <v>45727.6666666667</v>
       </c>
     </row>
     <row r="107">
@@ -22740,7 +22740,7 @@
         <v>45695</v>
       </c>
       <c r="F107" t="n">
-        <v>45695.79166666666</v>
+        <v>45695.7916666667</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>500</v>
       </c>
       <c r="L107" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>45700.79166666666</v>
+        <v>45700.7916666667</v>
       </c>
     </row>
     <row r="108">
@@ -23115,7 +23115,7 @@
         <v>45726</v>
       </c>
       <c r="F112" t="n">
-        <v>45726.79166666666</v>
+        <v>45726.7916666667</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>500</v>
       </c>
       <c r="L112" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>45732.79166666666</v>
+        <v>45732.7916666667</v>
       </c>
     </row>
     <row r="113">
@@ -23190,7 +23190,7 @@
         <v>45719</v>
       </c>
       <c r="F113" t="n">
-        <v>45719.79166666666</v>
+        <v>45719.7916666667</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>250</v>
       </c>
       <c r="L113" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>45733.79166666666</v>
+        <v>45733.7916666667</v>
       </c>
     </row>
     <row r="114">
@@ -23265,7 +23265,7 @@
         <v>45699</v>
       </c>
       <c r="F114" t="n">
-        <v>45699.45833333334</v>
+        <v>45699.4583333333</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>400</v>
       </c>
       <c r="L114" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>45702.45833333334</v>
+        <v>45702.4583333333</v>
       </c>
     </row>
     <row r="115">
@@ -23340,7 +23340,7 @@
         <v>45698</v>
       </c>
       <c r="F115" t="n">
-        <v>45698.70833333334</v>
+        <v>45698.7083333333</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>500</v>
       </c>
       <c r="L115" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>45708.70833333334</v>
+        <v>45708.7083333333</v>
       </c>
     </row>
     <row r="116">
@@ -23490,7 +23490,7 @@
         <v>45697</v>
       </c>
       <c r="F117" t="n">
-        <v>45697.45833333334</v>
+        <v>45697.4583333333</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>1000</v>
       </c>
       <c r="L117" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>45704.45833333334</v>
+        <v>45704.4583333333</v>
       </c>
     </row>
     <row r="118">
@@ -23790,7 +23790,7 @@
         <v>45699</v>
       </c>
       <c r="F121" t="n">
-        <v>45699.54166666666</v>
+        <v>45699.5416666667</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>400</v>
       </c>
       <c r="L121" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>45715.54166666666</v>
+        <v>45715.5416666667</v>
       </c>
     </row>
     <row r="122">
@@ -23940,7 +23940,7 @@
         <v>45689</v>
       </c>
       <c r="F123" t="n">
-        <v>45689.83333333334</v>
+        <v>45689.8333333333</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>1000</v>
       </c>
       <c r="L123" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>45705.83333333334</v>
+        <v>45705.8333333333</v>
       </c>
     </row>
     <row r="124">
@@ -24090,7 +24090,7 @@
         <v>45699</v>
       </c>
       <c r="F125" t="n">
-        <v>45699.79166666666</v>
+        <v>45699.7916666667</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>500</v>
       </c>
       <c r="L125" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>45713.79166666666</v>
+        <v>45713.7916666667</v>
       </c>
     </row>
     <row r="126">
@@ -24240,7 +24240,7 @@
         <v>45706</v>
       </c>
       <c r="F127" t="n">
-        <v>45706.66666666666</v>
+        <v>45706.6666666667</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -24266,7 +24266,7 @@
         <v>650</v>
       </c>
       <c r="L127" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M127" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>45717.66666666666</v>
+        <v>45717.6666666667</v>
       </c>
     </row>
     <row r="128">
@@ -24315,7 +24315,7 @@
         <v>45692</v>
       </c>
       <c r="F128" t="n">
-        <v>45692.58333333334</v>
+        <v>45692.5833333333</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>500</v>
       </c>
       <c r="L128" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>45701.58333333334</v>
+        <v>45701.5833333333</v>
       </c>
     </row>
     <row r="129">
@@ -24390,7 +24390,7 @@
         <v>45701</v>
       </c>
       <c r="F129" t="n">
-        <v>45701.54166666666</v>
+        <v>45701.5416666667</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>650</v>
       </c>
       <c r="L129" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>45709.54166666666</v>
+        <v>45709.5416666667</v>
       </c>
     </row>
     <row r="130">
@@ -24540,7 +24540,7 @@
         <v>45713</v>
       </c>
       <c r="F131" t="n">
-        <v>45713.70833333334</v>
+        <v>45713.7083333333</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>400</v>
       </c>
       <c r="L131" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>45733.70833333334</v>
+        <v>45733.7083333333</v>
       </c>
     </row>
     <row r="132">
@@ -24615,7 +24615,7 @@
         <v>45713</v>
       </c>
       <c r="F132" t="n">
-        <v>45713.58333333334</v>
+        <v>45713.5833333333</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>650</v>
       </c>
       <c r="L132" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>45723.58333333334</v>
+        <v>45723.5833333333</v>
       </c>
     </row>
     <row r="133">
@@ -24690,7 +24690,7 @@
         <v>45698</v>
       </c>
       <c r="F133" t="n">
-        <v>45698.45833333334</v>
+        <v>45698.4583333333</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>10</v>
       </c>
       <c r="L133" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>45702.45833333334</v>
+        <v>45702.4583333333</v>
       </c>
     </row>
     <row r="134">
@@ -24765,7 +24765,7 @@
         <v>45698</v>
       </c>
       <c r="F134" t="n">
-        <v>45698.66666666666</v>
+        <v>45698.6666666667</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>500</v>
       </c>
       <c r="L134" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>45705.66666666666</v>
+        <v>45705.6666666667</v>
       </c>
     </row>
     <row r="135">
@@ -24840,7 +24840,7 @@
         <v>45691</v>
       </c>
       <c r="F135" t="n">
-        <v>45691.54166666666</v>
+        <v>45691.5416666667</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>250</v>
       </c>
       <c r="L135" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>45700.54166666666</v>
+        <v>45700.5416666667</v>
       </c>
     </row>
     <row r="136">
@@ -24990,7 +24990,7 @@
         <v>45717</v>
       </c>
       <c r="F137" t="n">
-        <v>45717.83333333334</v>
+        <v>45717.8333333333</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>500</v>
       </c>
       <c r="L137" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>45721.83333333334</v>
+        <v>45721.8333333333</v>
       </c>
     </row>
     <row r="138">
@@ -25065,7 +25065,7 @@
         <v>45715</v>
       </c>
       <c r="F138" t="n">
-        <v>45715.83333333334</v>
+        <v>45715.8333333333</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>250</v>
       </c>
       <c r="L138" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>45725.83333333334</v>
+        <v>45725.8333333333</v>
       </c>
     </row>
     <row r="139">
@@ -25140,7 +25140,7 @@
         <v>45704</v>
       </c>
       <c r="F139" t="n">
-        <v>45704.45833333334</v>
+        <v>45704.4583333333</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>250</v>
       </c>
       <c r="L139" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M139" t="inlineStr">
         <is>
@@ -25189,7 +25189,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>45723.45833333334</v>
+        <v>45723.4583333333</v>
       </c>
     </row>
     <row r="140">
@@ -25215,7 +25215,7 @@
         <v>45725</v>
       </c>
       <c r="F140" t="n">
-        <v>45725.54166666666</v>
+        <v>45725.5416666667</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>400</v>
       </c>
       <c r="L140" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>45743.54166666666</v>
+        <v>45743.5416666667</v>
       </c>
     </row>
     <row r="141">
@@ -25365,7 +25365,7 @@
         <v>45703</v>
       </c>
       <c r="F142" t="n">
-        <v>45703.83333333334</v>
+        <v>45703.8333333333</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>10</v>
       </c>
       <c r="L142" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>45714.83333333334</v>
+        <v>45714.8333333333</v>
       </c>
     </row>
     <row r="143">
@@ -25440,7 +25440,7 @@
         <v>45716</v>
       </c>
       <c r="F143" t="n">
-        <v>45716.41666666666</v>
+        <v>45716.4166666667</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>500</v>
       </c>
       <c r="L143" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>45722.41666666666</v>
+        <v>45722.4166666667</v>
       </c>
     </row>
     <row r="144">
@@ -25515,7 +25515,7 @@
         <v>45709</v>
       </c>
       <c r="F144" t="n">
-        <v>45709.70833333334</v>
+        <v>45709.7083333333</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>250</v>
       </c>
       <c r="L144" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>45722.70833333334</v>
+        <v>45722.7083333333</v>
       </c>
     </row>
     <row r="145">
@@ -25590,7 +25590,7 @@
         <v>45716</v>
       </c>
       <c r="F145" t="n">
-        <v>45716.58333333334</v>
+        <v>45716.5833333333</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>250</v>
       </c>
       <c r="L145" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>45735.58333333334</v>
+        <v>45735.5833333333</v>
       </c>
     </row>
     <row r="146">
@@ -25665,7 +25665,7 @@
         <v>45721</v>
       </c>
       <c r="F146" t="n">
-        <v>45721.41666666666</v>
+        <v>45721.4166666667</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>650</v>
       </c>
       <c r="L146" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>45728.41666666666</v>
+        <v>45728.4166666667</v>
       </c>
     </row>
     <row r="147">
@@ -25740,7 +25740,7 @@
         <v>45709</v>
       </c>
       <c r="F147" t="n">
-        <v>45709.41666666666</v>
+        <v>45709.4166666667</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>500</v>
       </c>
       <c r="L147" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>45725.41666666666</v>
+        <v>45725.4166666667</v>
       </c>
     </row>
     <row r="148">
@@ -25815,7 +25815,7 @@
         <v>45703</v>
       </c>
       <c r="F148" t="n">
-        <v>45703.83333333334</v>
+        <v>45703.8333333333</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -25841,7 +25841,7 @@
         <v>400</v>
       </c>
       <c r="L148" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>45717.83333333334</v>
+        <v>45717.8333333333</v>
       </c>
     </row>
     <row r="149">
@@ -25890,7 +25890,7 @@
         <v>45724</v>
       </c>
       <c r="F149" t="n">
-        <v>45724.70833333334</v>
+        <v>45724.7083333333</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>10</v>
       </c>
       <c r="L149" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>45739.70833333334</v>
+        <v>45739.7083333333</v>
       </c>
     </row>
     <row r="150">
@@ -26040,7 +26040,7 @@
         <v>45719</v>
       </c>
       <c r="F151" t="n">
-        <v>45719.54166666666</v>
+        <v>45719.5416666667</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>500</v>
       </c>
       <c r="L151" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>45727.54166666666</v>
+        <v>45727.5416666667</v>
       </c>
     </row>
     <row r="152">
@@ -26115,7 +26115,7 @@
         <v>45729</v>
       </c>
       <c r="F152" t="n">
-        <v>45729.58333333334</v>
+        <v>45729.5833333333</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>10</v>
       </c>
       <c r="L152" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>45749.58333333334</v>
+        <v>45749.5833333333</v>
       </c>
     </row>
     <row r="153">
@@ -26190,7 +26190,7 @@
         <v>45709</v>
       </c>
       <c r="F153" t="n">
-        <v>45709.54166666666</v>
+        <v>45709.5416666667</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>1000</v>
       </c>
       <c r="L153" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>45720.54166666666</v>
+        <v>45720.5416666667</v>
       </c>
     </row>
     <row r="154">
@@ -26265,7 +26265,7 @@
         <v>45690</v>
       </c>
       <c r="F154" t="n">
-        <v>45690.45833333334</v>
+        <v>45690.4583333333</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -26291,7 +26291,7 @@
         <v>650</v>
       </c>
       <c r="L154" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>45705.45833333334</v>
+        <v>45705.4583333333</v>
       </c>
     </row>
     <row r="155">
@@ -26415,7 +26415,7 @@
         <v>45707</v>
       </c>
       <c r="F156" t="n">
-        <v>45707.66666666666</v>
+        <v>45707.6666666667</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>400</v>
       </c>
       <c r="L156" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>45715.66666666666</v>
+        <v>45715.6666666667</v>
       </c>
     </row>
     <row r="157">
@@ -26490,7 +26490,7 @@
         <v>45724</v>
       </c>
       <c r="F157" t="n">
-        <v>45724.54166666666</v>
+        <v>45724.5416666667</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>10</v>
       </c>
       <c r="L157" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>45740.54166666666</v>
+        <v>45740.5416666667</v>
       </c>
     </row>
     <row r="158">
@@ -26565,7 +26565,7 @@
         <v>45724</v>
       </c>
       <c r="F158" t="n">
-        <v>45724.83333333334</v>
+        <v>45724.8333333333</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>500</v>
       </c>
       <c r="L158" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -26614,7 +26614,7 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>45731.83333333334</v>
+        <v>45731.8333333333</v>
       </c>
     </row>
     <row r="159">
@@ -26640,7 +26640,7 @@
         <v>45713</v>
       </c>
       <c r="F159" t="n">
-        <v>45713.45833333334</v>
+        <v>45713.4583333333</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>1000</v>
       </c>
       <c r="L159" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>45726.45833333334</v>
+        <v>45726.4583333333</v>
       </c>
     </row>
     <row r="160">
@@ -26790,7 +26790,7 @@
         <v>45690</v>
       </c>
       <c r="F161" t="n">
-        <v>45690.41666666666</v>
+        <v>45690.4166666667</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
         <v>500</v>
       </c>
       <c r="L161" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>45695.41666666666</v>
+        <v>45695.4166666667</v>
       </c>
     </row>
     <row r="162">
@@ -26940,7 +26940,7 @@
         <v>45716</v>
       </c>
       <c r="F163" t="n">
-        <v>45716.41666666666</v>
+        <v>45716.4166666667</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>1000</v>
       </c>
       <c r="L163" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>45729.41666666666</v>
+        <v>45729.4166666667</v>
       </c>
     </row>
     <row r="164">
@@ -27015,7 +27015,7 @@
         <v>45719</v>
       </c>
       <c r="F164" t="n">
-        <v>45719.79166666666</v>
+        <v>45719.7916666667</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>650</v>
       </c>
       <c r="L164" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>45737.79166666666</v>
+        <v>45737.7916666667</v>
       </c>
     </row>
     <row r="165">
@@ -27090,7 +27090,7 @@
         <v>45708</v>
       </c>
       <c r="F165" t="n">
-        <v>45708.58333333334</v>
+        <v>45708.5833333333</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>10</v>
       </c>
       <c r="L165" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>45728.58333333334</v>
+        <v>45728.5833333333</v>
       </c>
     </row>
     <row r="166">
@@ -27315,7 +27315,7 @@
         <v>45715</v>
       </c>
       <c r="F168" t="n">
-        <v>45715.66666666666</v>
+        <v>45715.6666666667</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>400</v>
       </c>
       <c r="L168" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>45730.66666666666</v>
+        <v>45730.6666666667</v>
       </c>
     </row>
     <row r="169">
@@ -27540,7 +27540,7 @@
         <v>45717</v>
       </c>
       <c r="F171" t="n">
-        <v>45717.54166666666</v>
+        <v>45717.5416666667</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>250</v>
       </c>
       <c r="L171" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>45737.54166666666</v>
+        <v>45737.5416666667</v>
       </c>
     </row>
     <row r="172">
@@ -27615,7 +27615,7 @@
         <v>45697</v>
       </c>
       <c r="F172" t="n">
-        <v>45697.58333333334</v>
+        <v>45697.5833333333</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>500</v>
       </c>
       <c r="L172" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M172" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>45717.58333333334</v>
+        <v>45717.5833333333</v>
       </c>
     </row>
     <row r="173">
@@ -27765,7 +27765,7 @@
         <v>45715</v>
       </c>
       <c r="F174" t="n">
-        <v>45715.79166666666</v>
+        <v>45715.7916666667</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>250</v>
       </c>
       <c r="L174" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>45719.79166666666</v>
+        <v>45719.7916666667</v>
       </c>
     </row>
     <row r="175">
@@ -27990,7 +27990,7 @@
         <v>45705</v>
       </c>
       <c r="F177" t="n">
-        <v>45705.54166666666</v>
+        <v>45705.5416666667</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>400</v>
       </c>
       <c r="L177" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M177" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>45712.54166666666</v>
+        <v>45712.5416666667</v>
       </c>
     </row>
     <row r="178">
@@ -28065,7 +28065,7 @@
         <v>45702</v>
       </c>
       <c r="F178" t="n">
-        <v>45702.45833333334</v>
+        <v>45702.4583333333</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>10</v>
       </c>
       <c r="L178" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>45717.45833333334</v>
+        <v>45717.4583333333</v>
       </c>
     </row>
     <row r="179">
@@ -28140,7 +28140,7 @@
         <v>45690</v>
       </c>
       <c r="F179" t="n">
-        <v>45690.79166666666</v>
+        <v>45690.7916666667</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -28166,7 +28166,7 @@
         <v>500</v>
       </c>
       <c r="L179" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>45707.79166666666</v>
+        <v>45707.7916666667</v>
       </c>
     </row>
     <row r="180">
@@ -28215,7 +28215,7 @@
         <v>45705</v>
       </c>
       <c r="F180" t="n">
-        <v>45705.45833333334</v>
+        <v>45705.4583333333</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>400</v>
       </c>
       <c r="L180" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>45723.45833333334</v>
+        <v>45723.4583333333</v>
       </c>
     </row>
     <row r="181">
@@ -28290,7 +28290,7 @@
         <v>45706</v>
       </c>
       <c r="F181" t="n">
-        <v>45706.41666666666</v>
+        <v>45706.4166666667</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>650</v>
       </c>
       <c r="L181" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>45716.41666666666</v>
+        <v>45716.4166666667</v>
       </c>
     </row>
     <row r="182">
@@ -28440,7 +28440,7 @@
         <v>45699</v>
       </c>
       <c r="F183" t="n">
-        <v>45699.66666666666</v>
+        <v>45699.6666666667</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>250</v>
       </c>
       <c r="L183" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>45711.66666666666</v>
+        <v>45711.6666666667</v>
       </c>
     </row>
     <row r="184">
@@ -28515,7 +28515,7 @@
         <v>45690</v>
       </c>
       <c r="F184" t="n">
-        <v>45690.79166666666</v>
+        <v>45690.7916666667</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>250</v>
       </c>
       <c r="L184" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M184" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>45701.79166666666</v>
+        <v>45701.7916666667</v>
       </c>
     </row>
     <row r="185">
@@ -28590,7 +28590,7 @@
         <v>45709</v>
       </c>
       <c r="F185" t="n">
-        <v>45709.54166666666</v>
+        <v>45709.5416666667</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>650</v>
       </c>
       <c r="L185" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>45724.54166666666</v>
+        <v>45724.5416666667</v>
       </c>
     </row>
     <row r="186">
@@ -28665,7 +28665,7 @@
         <v>45695</v>
       </c>
       <c r="F186" t="n">
-        <v>45695.54166666666</v>
+        <v>45695.5416666667</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>1000</v>
       </c>
       <c r="L186" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>45703.54166666666</v>
+        <v>45703.5416666667</v>
       </c>
     </row>
     <row r="187">
@@ -28890,7 +28890,7 @@
         <v>45701</v>
       </c>
       <c r="F189" t="n">
-        <v>45701.79166666666</v>
+        <v>45701.7916666667</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>400</v>
       </c>
       <c r="L189" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>45713.79166666666</v>
+        <v>45713.7916666667</v>
       </c>
     </row>
     <row r="190">
@@ -28965,7 +28965,7 @@
         <v>45690</v>
       </c>
       <c r="F190" t="n">
-        <v>45690.58333333334</v>
+        <v>45690.5833333333</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>10</v>
       </c>
       <c r="L190" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>45697.58333333334</v>
+        <v>45697.5833333333</v>
       </c>
     </row>
     <row r="191">
@@ -29115,7 +29115,7 @@
         <v>45698</v>
       </c>
       <c r="F192" t="n">
-        <v>45698.70833333334</v>
+        <v>45698.7083333333</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>400</v>
       </c>
       <c r="L192" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>45708.70833333334</v>
+        <v>45708.7083333333</v>
       </c>
     </row>
     <row r="193">
@@ -29340,7 +29340,7 @@
         <v>45727</v>
       </c>
       <c r="F195" t="n">
-        <v>45727.41666666666</v>
+        <v>45727.4166666667</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>500</v>
       </c>
       <c r="L195" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>45738.41666666666</v>
+        <v>45738.4166666667</v>
       </c>
     </row>
     <row r="196">
@@ -29415,7 +29415,7 @@
         <v>45690</v>
       </c>
       <c r="F196" t="n">
-        <v>45690.79166666666</v>
+        <v>45690.7916666667</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>650</v>
       </c>
       <c r="L196" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>45698.79166666666</v>
+        <v>45698.7916666667</v>
       </c>
     </row>
     <row r="197">
@@ -29490,7 +29490,7 @@
         <v>45713</v>
       </c>
       <c r="F197" t="n">
-        <v>45713.45833333334</v>
+        <v>45713.4583333333</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>1000</v>
       </c>
       <c r="L197" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>45721.45833333334</v>
+        <v>45721.4583333333</v>
       </c>
     </row>
     <row r="198">
@@ -29565,7 +29565,7 @@
         <v>45711</v>
       </c>
       <c r="F198" t="n">
-        <v>45711.45833333334</v>
+        <v>45711.4583333333</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>650</v>
       </c>
       <c r="L198" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>45729.45833333334</v>
+        <v>45729.4583333333</v>
       </c>
     </row>
     <row r="199">
@@ -29640,7 +29640,7 @@
         <v>45722</v>
       </c>
       <c r="F199" t="n">
-        <v>45722.58333333334</v>
+        <v>45722.5833333333</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>500</v>
       </c>
       <c r="L199" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>45732.58333333334</v>
+        <v>45732.5833333333</v>
       </c>
     </row>
     <row r="200">
@@ -29715,7 +29715,7 @@
         <v>45694</v>
       </c>
       <c r="F200" t="n">
-        <v>45694.45833333334</v>
+        <v>45694.4583333333</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>500</v>
       </c>
       <c r="L200" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>45712.45833333334</v>
+        <v>45712.4583333333</v>
       </c>
     </row>
     <row r="201">
@@ -29865,7 +29865,7 @@
         <v>45720</v>
       </c>
       <c r="F202" t="n">
-        <v>45720.58333333334</v>
+        <v>45720.5833333333</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -29891,7 +29891,7 @@
         <v>400</v>
       </c>
       <c r="L202" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>45730.58333333334</v>
+        <v>45730.5833333333</v>
       </c>
     </row>
     <row r="203">
@@ -29940,7 +29940,7 @@
         <v>45701</v>
       </c>
       <c r="F203" t="n">
-        <v>45701.66666666666</v>
+        <v>45701.6666666667</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -29966,7 +29966,7 @@
         <v>10</v>
       </c>
       <c r="L203" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M203" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>45704.66666666666</v>
+        <v>45704.6666666667</v>
       </c>
     </row>
     <row r="204">
@@ -30165,7 +30165,7 @@
         <v>45724</v>
       </c>
       <c r="F206" t="n">
-        <v>45724.41666666666</v>
+        <v>45724.4166666667</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>1000</v>
       </c>
       <c r="L206" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>45729.41666666666</v>
+        <v>45729.4166666667</v>
       </c>
     </row>
     <row r="207">
@@ -30240,7 +30240,7 @@
         <v>45707</v>
       </c>
       <c r="F207" t="n">
-        <v>45707.54166666666</v>
+        <v>45707.5416666667</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>650</v>
       </c>
       <c r="L207" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>45725.54166666666</v>
+        <v>45725.5416666667</v>
       </c>
     </row>
     <row r="208">
@@ -30315,7 +30315,7 @@
         <v>45691</v>
       </c>
       <c r="F208" t="n">
-        <v>45691.79166666666</v>
+        <v>45691.7916666667</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>1000</v>
       </c>
       <c r="L208" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>45711.79166666666</v>
+        <v>45711.7916666667</v>
       </c>
     </row>
     <row r="209">
@@ -30390,7 +30390,7 @@
         <v>45702</v>
       </c>
       <c r="F209" t="n">
-        <v>45702.83333333334</v>
+        <v>45702.8333333333</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>250</v>
       </c>
       <c r="L209" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
@@ -30439,7 +30439,7 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>45720.83333333334</v>
+        <v>45720.8333333333</v>
       </c>
     </row>
     <row r="210">
@@ -30540,7 +30540,7 @@
         <v>45729</v>
       </c>
       <c r="F211" t="n">
-        <v>45729.45833333334</v>
+        <v>45729.4583333333</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -30566,7 +30566,7 @@
         <v>650</v>
       </c>
       <c r="L211" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M211" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>45732.45833333334</v>
+        <v>45732.4583333333</v>
       </c>
     </row>
     <row r="212">
@@ -30615,7 +30615,7 @@
         <v>45706</v>
       </c>
       <c r="F212" t="n">
-        <v>45706.54166666666</v>
+        <v>45706.5416666667</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>500</v>
       </c>
       <c r="L212" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>45721.54166666666</v>
+        <v>45721.5416666667</v>
       </c>
     </row>
     <row r="213">
@@ -30690,7 +30690,7 @@
         <v>45725</v>
       </c>
       <c r="F213" t="n">
-        <v>45725.41666666666</v>
+        <v>45725.4166666667</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>10</v>
       </c>
       <c r="L213" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>45732.41666666666</v>
+        <v>45732.4166666667</v>
       </c>
     </row>
     <row r="214">
@@ -30765,7 +30765,7 @@
         <v>45715</v>
       </c>
       <c r="F214" t="n">
-        <v>45715.79166666666</v>
+        <v>45715.7916666667</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>250</v>
       </c>
       <c r="L214" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M214" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>45722.79166666666</v>
+        <v>45722.7916666667</v>
       </c>
     </row>
     <row r="215">
@@ -30915,7 +30915,7 @@
         <v>45728</v>
       </c>
       <c r="F216" t="n">
-        <v>45728.45833333334</v>
+        <v>45728.4583333333</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>250</v>
       </c>
       <c r="L216" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M216" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>45747.45833333334</v>
+        <v>45747.4583333333</v>
       </c>
     </row>
     <row r="217">
@@ -31215,7 +31215,7 @@
         <v>45696</v>
       </c>
       <c r="F220" t="n">
-        <v>45696.41666666666</v>
+        <v>45696.4166666667</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>1000</v>
       </c>
       <c r="L220" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
@@ -31264,7 +31264,7 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>45704.41666666666</v>
+        <v>45704.4166666667</v>
       </c>
     </row>
     <row r="221">
@@ -31290,7 +31290,7 @@
         <v>45692</v>
       </c>
       <c r="F221" t="n">
-        <v>45692.83333333334</v>
+        <v>45692.8333333333</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>500</v>
       </c>
       <c r="L221" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>45709.83333333334</v>
+        <v>45709.8333333333</v>
       </c>
     </row>
     <row r="222">
@@ -31590,7 +31590,7 @@
         <v>45710</v>
       </c>
       <c r="F225" t="n">
-        <v>45710.58333333334</v>
+        <v>45710.5833333333</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>500</v>
       </c>
       <c r="L225" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M225" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>45718.58333333334</v>
+        <v>45718.5833333333</v>
       </c>
     </row>
     <row r="226">
@@ -31740,7 +31740,7 @@
         <v>45700</v>
       </c>
       <c r="F227" t="n">
-        <v>45700.83333333334</v>
+        <v>45700.8333333333</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -31766,7 +31766,7 @@
         <v>500</v>
       </c>
       <c r="L227" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>45718.83333333334</v>
+        <v>45718.8333333333</v>
       </c>
     </row>
     <row r="228">
@@ -32040,7 +32040,7 @@
         <v>45698</v>
       </c>
       <c r="F231" t="n">
-        <v>45698.79166666666</v>
+        <v>45698.7916666667</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>650</v>
       </c>
       <c r="L231" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>45717.79166666666</v>
+        <v>45717.7916666667</v>
       </c>
     </row>
     <row r="232">
@@ -32115,7 +32115,7 @@
         <v>45698</v>
       </c>
       <c r="F232" t="n">
-        <v>45698.83333333334</v>
+        <v>45698.8333333333</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>250</v>
       </c>
       <c r="L232" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M232" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>45702.83333333334</v>
+        <v>45702.8333333333</v>
       </c>
     </row>
     <row r="233">
@@ -32265,7 +32265,7 @@
         <v>45700</v>
       </c>
       <c r="F234" t="n">
-        <v>45700.66666666666</v>
+        <v>45700.6666666667</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>250</v>
       </c>
       <c r="L234" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
@@ -32314,7 +32314,7 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>45720.66666666666</v>
+        <v>45720.6666666667</v>
       </c>
     </row>
     <row r="235">
@@ -32340,7 +32340,7 @@
         <v>45701</v>
       </c>
       <c r="F235" t="n">
-        <v>45701.70833333334</v>
+        <v>45701.7083333333</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>1000</v>
       </c>
       <c r="L235" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>45706.70833333334</v>
+        <v>45706.7083333333</v>
       </c>
     </row>
     <row r="236">
@@ -32415,7 +32415,7 @@
         <v>45698</v>
       </c>
       <c r="F236" t="n">
-        <v>45698.45833333334</v>
+        <v>45698.4583333333</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>250</v>
       </c>
       <c r="L236" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
@@ -32464,7 +32464,7 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>45711.45833333334</v>
+        <v>45711.4583333333</v>
       </c>
     </row>
     <row r="237">
@@ -32490,7 +32490,7 @@
         <v>45700</v>
       </c>
       <c r="F237" t="n">
-        <v>45700.41666666666</v>
+        <v>45700.4166666667</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>10</v>
       </c>
       <c r="L237" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>45718.41666666666</v>
+        <v>45718.4166666667</v>
       </c>
     </row>
     <row r="238">
@@ -32565,7 +32565,7 @@
         <v>45693</v>
       </c>
       <c r="F238" t="n">
-        <v>45693.41666666666</v>
+        <v>45693.4166666667</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>500</v>
       </c>
       <c r="L238" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>45707.41666666666</v>
+        <v>45707.4166666667</v>
       </c>
     </row>
     <row r="239">
@@ -32715,7 +32715,7 @@
         <v>45694</v>
       </c>
       <c r="F240" t="n">
-        <v>45694.66666666666</v>
+        <v>45694.6666666667</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>400</v>
       </c>
       <c r="L240" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>45705.66666666666</v>
+        <v>45705.6666666667</v>
       </c>
     </row>
     <row r="241">
@@ -32790,7 +32790,7 @@
         <v>45722</v>
       </c>
       <c r="F241" t="n">
-        <v>45722.66666666666</v>
+        <v>45722.6666666667</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>250</v>
       </c>
       <c r="L241" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
@@ -32839,7 +32839,7 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>45738.66666666666</v>
+        <v>45738.6666666667</v>
       </c>
     </row>
     <row r="242">
@@ -32940,7 +32940,7 @@
         <v>45692</v>
       </c>
       <c r="F243" t="n">
-        <v>45692.54166666666</v>
+        <v>45692.5416666667</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>500</v>
       </c>
       <c r="L243" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>45712.54166666666</v>
+        <v>45712.5416666667</v>
       </c>
     </row>
     <row r="244">
@@ -33090,7 +33090,7 @@
         <v>45708</v>
       </c>
       <c r="F245" t="n">
-        <v>45708.58333333334</v>
+        <v>45708.5833333333</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>500</v>
       </c>
       <c r="L245" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>45722.58333333334</v>
+        <v>45722.5833333333</v>
       </c>
     </row>
     <row r="246">
@@ -33165,7 +33165,7 @@
         <v>45715</v>
       </c>
       <c r="F246" t="n">
-        <v>45715.58333333334</v>
+        <v>45715.5833333333</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>500</v>
       </c>
       <c r="L246" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>45719.58333333334</v>
+        <v>45719.5833333333</v>
       </c>
     </row>
     <row r="247">
@@ -33240,7 +33240,7 @@
         <v>45729</v>
       </c>
       <c r="F247" t="n">
-        <v>45729.66666666666</v>
+        <v>45729.6666666667</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>500</v>
       </c>
       <c r="L247" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>45746.66666666666</v>
+        <v>45746.6666666667</v>
       </c>
     </row>
     <row r="248">
@@ -33315,7 +33315,7 @@
         <v>45689</v>
       </c>
       <c r="F248" t="n">
-        <v>45689.70833333334</v>
+        <v>45689.7083333333</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>1000</v>
       </c>
       <c r="L248" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>45699.70833333334</v>
+        <v>45699.7083333333</v>
       </c>
     </row>
     <row r="249">
@@ -33390,7 +33390,7 @@
         <v>45708</v>
       </c>
       <c r="F249" t="n">
-        <v>45708.45833333334</v>
+        <v>45708.4583333333</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>650</v>
       </c>
       <c r="L249" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>45715.45833333334</v>
+        <v>45715.4583333333</v>
       </c>
     </row>
     <row r="250">
@@ -33765,7 +33765,7 @@
         <v>45716</v>
       </c>
       <c r="F254" t="n">
-        <v>45716.70833333334</v>
+        <v>45716.7083333333</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>400</v>
       </c>
       <c r="L254" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>45728.70833333334</v>
+        <v>45728.7083333333</v>
       </c>
     </row>
     <row r="255">
@@ -33840,7 +33840,7 @@
         <v>45691</v>
       </c>
       <c r="F255" t="n">
-        <v>45691.45833333334</v>
+        <v>45691.4583333333</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -33866,7 +33866,7 @@
         <v>250</v>
       </c>
       <c r="L255" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>45704.45833333334</v>
+        <v>45704.4583333333</v>
       </c>
     </row>
     <row r="256">
@@ -33915,7 +33915,7 @@
         <v>45728</v>
       </c>
       <c r="F256" t="n">
-        <v>45728.45833333334</v>
+        <v>45728.4583333333</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>400</v>
       </c>
       <c r="L256" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>45742.45833333334</v>
+        <v>45742.4583333333</v>
       </c>
     </row>
     <row r="257">
@@ -33990,7 +33990,7 @@
         <v>45712</v>
       </c>
       <c r="F257" t="n">
-        <v>45712.45833333334</v>
+        <v>45712.4583333333</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>10</v>
       </c>
       <c r="L257" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>45716.45833333334</v>
+        <v>45716.4583333333</v>
       </c>
     </row>
     <row r="258">
@@ -34215,7 +34215,7 @@
         <v>45720</v>
       </c>
       <c r="F260" t="n">
-        <v>45720.41666666666</v>
+        <v>45720.4166666667</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>500</v>
       </c>
       <c r="L260" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>45737.41666666666</v>
+        <v>45737.4166666667</v>
       </c>
     </row>
     <row r="261">
@@ -34290,7 +34290,7 @@
         <v>45690</v>
       </c>
       <c r="F261" t="n">
-        <v>45690.70833333334</v>
+        <v>45690.7083333333</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -34316,7 +34316,7 @@
         <v>500</v>
       </c>
       <c r="L261" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>45706.70833333334</v>
+        <v>45706.7083333333</v>
       </c>
     </row>
     <row r="262">
@@ -34365,7 +34365,7 @@
         <v>45722</v>
       </c>
       <c r="F262" t="n">
-        <v>45722.83333333334</v>
+        <v>45722.8333333333</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>250</v>
       </c>
       <c r="L262" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M262" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>45727.83333333334</v>
+        <v>45727.8333333333</v>
       </c>
     </row>
     <row r="263">
@@ -34515,7 +34515,7 @@
         <v>45693</v>
       </c>
       <c r="F264" t="n">
-        <v>45693.45833333334</v>
+        <v>45693.4583333333</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>400</v>
       </c>
       <c r="L264" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
@@ -34564,7 +34564,7 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>45713.45833333334</v>
+        <v>45713.4583333333</v>
       </c>
     </row>
     <row r="265">
@@ -34665,7 +34665,7 @@
         <v>45722</v>
       </c>
       <c r="F266" t="n">
-        <v>45722.41666666666</v>
+        <v>45722.4166666667</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>250</v>
       </c>
       <c r="L266" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>45726.41666666666</v>
+        <v>45726.4166666667</v>
       </c>
     </row>
     <row r="267">
@@ -34815,7 +34815,7 @@
         <v>45705</v>
       </c>
       <c r="F268" t="n">
-        <v>45705.45833333334</v>
+        <v>45705.4583333333</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>10</v>
       </c>
       <c r="L268" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
@@ -34864,7 +34864,7 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>45725.45833333334</v>
+        <v>45725.4583333333</v>
       </c>
     </row>
     <row r="269">
@@ -34965,7 +34965,7 @@
         <v>45709</v>
       </c>
       <c r="F270" t="n">
-        <v>45709.66666666666</v>
+        <v>45709.6666666667</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
         <v>1000</v>
       </c>
       <c r="L270" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M270" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>45713.66666666666</v>
+        <v>45713.6666666667</v>
       </c>
     </row>
     <row r="271">
@@ -35040,7 +35040,7 @@
         <v>45725</v>
       </c>
       <c r="F271" t="n">
-        <v>45725.45833333334</v>
+        <v>45725.4583333333</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>650</v>
       </c>
       <c r="L271" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>45738.45833333334</v>
+        <v>45738.4583333333</v>
       </c>
     </row>
     <row r="272">
@@ -35115,7 +35115,7 @@
         <v>45709</v>
       </c>
       <c r="F272" t="n">
-        <v>45709.70833333334</v>
+        <v>45709.7083333333</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -35141,7 +35141,7 @@
         <v>400</v>
       </c>
       <c r="L272" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>45714.70833333334</v>
+        <v>45714.7083333333</v>
       </c>
     </row>
     <row r="273">
@@ -35340,7 +35340,7 @@
         <v>45695</v>
       </c>
       <c r="F275" t="n">
-        <v>45695.45833333334</v>
+        <v>45695.4583333333</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>500</v>
       </c>
       <c r="L275" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M275" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>45698.45833333334</v>
+        <v>45698.4583333333</v>
       </c>
     </row>
     <row r="276">
@@ -35490,7 +35490,7 @@
         <v>45725</v>
       </c>
       <c r="F277" t="n">
-        <v>45725.79166666666</v>
+        <v>45725.7916666667</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>500</v>
       </c>
       <c r="L277" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>45735.79166666666</v>
+        <v>45735.7916666667</v>
       </c>
     </row>
     <row r="278">
@@ -35715,7 +35715,7 @@
         <v>45709</v>
       </c>
       <c r="F280" t="n">
-        <v>45709.54166666666</v>
+        <v>45709.5416666667</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>250</v>
       </c>
       <c r="L280" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>45725.54166666666</v>
+        <v>45725.5416666667</v>
       </c>
     </row>
     <row r="281">
@@ -35790,7 +35790,7 @@
         <v>45698</v>
       </c>
       <c r="F281" t="n">
-        <v>45698.41666666666</v>
+        <v>45698.4166666667</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>500</v>
       </c>
       <c r="L281" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>45706.41666666666</v>
+        <v>45706.4166666667</v>
       </c>
     </row>
     <row r="282">
@@ -35940,7 +35940,7 @@
         <v>45713</v>
       </c>
       <c r="F283" t="n">
-        <v>45713.79166666666</v>
+        <v>45713.7916666667</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>1000</v>
       </c>
       <c r="L283" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M283" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>45721.79166666666</v>
+        <v>45721.7916666667</v>
       </c>
     </row>
     <row r="284">
@@ -36015,7 +36015,7 @@
         <v>45709</v>
       </c>
       <c r="F284" t="n">
-        <v>45709.70833333334</v>
+        <v>45709.7083333333</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>500</v>
       </c>
       <c r="L284" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M284" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>45712.70833333334</v>
+        <v>45712.7083333333</v>
       </c>
     </row>
     <row r="285">
@@ -36165,7 +36165,7 @@
         <v>45713</v>
       </c>
       <c r="F286" t="n">
-        <v>45713.79166666666</v>
+        <v>45713.7916666667</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>1000</v>
       </c>
       <c r="L286" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M286" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>45728.79166666666</v>
+        <v>45728.7916666667</v>
       </c>
     </row>
     <row r="287">
@@ -36315,7 +36315,7 @@
         <v>45689</v>
       </c>
       <c r="F288" t="n">
-        <v>45689.58333333334</v>
+        <v>45689.5833333333</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>400</v>
       </c>
       <c r="L288" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M288" t="inlineStr">
         <is>
@@ -36364,7 +36364,7 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>45701.58333333334</v>
+        <v>45701.5833333333</v>
       </c>
     </row>
     <row r="289">
@@ -36390,7 +36390,7 @@
         <v>45714</v>
       </c>
       <c r="F289" t="n">
-        <v>45714.79166666666</v>
+        <v>45714.7916666667</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>500</v>
       </c>
       <c r="L289" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M289" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>45724.79166666666</v>
+        <v>45724.7916666667</v>
       </c>
     </row>
     <row r="290">
@@ -36540,7 +36540,7 @@
         <v>45692</v>
       </c>
       <c r="F291" t="n">
-        <v>45692.41666666666</v>
+        <v>45692.4166666667</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -36566,7 +36566,7 @@
         <v>10</v>
       </c>
       <c r="L291" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>45700.41666666666</v>
+        <v>45700.4166666667</v>
       </c>
     </row>
     <row r="292">
@@ -36915,7 +36915,7 @@
         <v>45700</v>
       </c>
       <c r="F296" t="n">
-        <v>45700.45833333334</v>
+        <v>45700.4583333333</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>400</v>
       </c>
       <c r="L296" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>45705.45833333334</v>
+        <v>45705.4583333333</v>
       </c>
     </row>
     <row r="297">
@@ -37140,7 +37140,7 @@
         <v>45725</v>
       </c>
       <c r="F299" t="n">
-        <v>45725.66666666666</v>
+        <v>45725.6666666667</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>250</v>
       </c>
       <c r="L299" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>45732.66666666666</v>
+        <v>45732.6666666667</v>
       </c>
     </row>
     <row r="300">
@@ -37215,7 +37215,7 @@
         <v>45690</v>
       </c>
       <c r="F300" t="n">
-        <v>45690.58333333334</v>
+        <v>45690.5833333333</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>500</v>
       </c>
       <c r="L300" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M300" t="inlineStr">
         <is>
@@ -37264,7 +37264,7 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>45694.58333333334</v>
+        <v>45694.5833333333</v>
       </c>
     </row>
     <row r="301">
@@ -37290,7 +37290,7 @@
         <v>45714</v>
       </c>
       <c r="F301" t="n">
-        <v>45714.83333333334</v>
+        <v>45714.8333333333</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>650</v>
       </c>
       <c r="L301" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M301" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>45732.83333333334</v>
+        <v>45732.8333333333</v>
       </c>
     </row>
     <row r="302">
@@ -37515,7 +37515,7 @@
         <v>45701</v>
       </c>
       <c r="F304" t="n">
-        <v>45701.79166666666</v>
+        <v>45701.7916666667</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>10</v>
       </c>
       <c r="L304" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M304" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>45708.79166666666</v>
+        <v>45708.7916666667</v>
       </c>
     </row>
     <row r="305">
@@ -37740,7 +37740,7 @@
         <v>45705</v>
       </c>
       <c r="F307" t="n">
-        <v>45705.58333333334</v>
+        <v>45705.5833333333</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -37766,7 +37766,7 @@
         <v>500</v>
       </c>
       <c r="L307" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M307" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>45723.58333333334</v>
+        <v>45723.5833333333</v>
       </c>
     </row>
     <row r="308">
@@ -37815,7 +37815,7 @@
         <v>45699</v>
       </c>
       <c r="F308" t="n">
-        <v>45699.58333333334</v>
+        <v>45699.5833333333</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>500</v>
       </c>
       <c r="L308" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M308" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>45719.58333333334</v>
+        <v>45719.5833333333</v>
       </c>
     </row>
     <row r="309">
@@ -38040,7 +38040,7 @@
         <v>45694</v>
       </c>
       <c r="F311" t="n">
-        <v>45694.58333333334</v>
+        <v>45694.5833333333</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>250</v>
       </c>
       <c r="L311" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>45704.58333333334</v>
+        <v>45704.5833333333</v>
       </c>
     </row>
     <row r="312">
@@ -38265,7 +38265,7 @@
         <v>45724</v>
       </c>
       <c r="F314" t="n">
-        <v>45724.83333333334</v>
+        <v>45724.8333333333</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>10</v>
       </c>
       <c r="L314" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M314" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>45730.83333333334</v>
+        <v>45730.8333333333</v>
       </c>
     </row>
     <row r="315">
@@ -38340,7 +38340,7 @@
         <v>45714</v>
       </c>
       <c r="F315" t="n">
-        <v>45714.70833333334</v>
+        <v>45714.7083333333</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>500</v>
       </c>
       <c r="L315" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M315" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>45719.70833333334</v>
+        <v>45719.7083333333</v>
       </c>
     </row>
     <row r="316">
@@ -38490,7 +38490,7 @@
         <v>45716</v>
       </c>
       <c r="F317" t="n">
-        <v>45716.83333333334</v>
+        <v>45716.8333333333</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
@@ -38516,7 +38516,7 @@
         <v>250</v>
       </c>
       <c r="L317" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M317" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>45725.83333333334</v>
+        <v>45725.8333333333</v>
       </c>
     </row>
     <row r="318">
@@ -38640,7 +38640,7 @@
         <v>45694</v>
       </c>
       <c r="F319" t="n">
-        <v>45694.70833333334</v>
+        <v>45694.7083333333</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>10</v>
       </c>
       <c r="L319" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M319" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>45702.70833333334</v>
+        <v>45702.7083333333</v>
       </c>
     </row>
     <row r="320">
@@ -38715,7 +38715,7 @@
         <v>45704</v>
       </c>
       <c r="F320" t="n">
-        <v>45704.83333333334</v>
+        <v>45704.8333333333</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>400</v>
       </c>
       <c r="L320" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M320" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>45721.83333333334</v>
+        <v>45721.8333333333</v>
       </c>
     </row>
     <row r="321">
@@ -38865,7 +38865,7 @@
         <v>45711</v>
       </c>
       <c r="F322" t="n">
-        <v>45711.54166666666</v>
+        <v>45711.5416666667</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
@@ -38891,7 +38891,7 @@
         <v>400</v>
       </c>
       <c r="L322" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M322" t="inlineStr">
         <is>
@@ -38914,7 +38914,7 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>45719.54166666666</v>
+        <v>45719.5416666667</v>
       </c>
     </row>
     <row r="323">
@@ -38940,7 +38940,7 @@
         <v>45715</v>
       </c>
       <c r="F323" t="n">
-        <v>45715.58333333334</v>
+        <v>45715.5833333333</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>250</v>
       </c>
       <c r="L323" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M323" t="inlineStr">
         <is>
@@ -38989,7 +38989,7 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>45728.58333333334</v>
+        <v>45728.5833333333</v>
       </c>
     </row>
     <row r="324">
@@ -39015,7 +39015,7 @@
         <v>45701</v>
       </c>
       <c r="F324" t="n">
-        <v>45701.79166666666</v>
+        <v>45701.7916666667</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
@@ -39041,7 +39041,7 @@
         <v>500</v>
       </c>
       <c r="L324" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M324" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>45712.79166666666</v>
+        <v>45712.7916666667</v>
       </c>
     </row>
     <row r="325">
@@ -39090,7 +39090,7 @@
         <v>45713</v>
       </c>
       <c r="F325" t="n">
-        <v>45713.70833333334</v>
+        <v>45713.7083333333</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>400</v>
       </c>
       <c r="L325" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M325" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>45722.70833333334</v>
+        <v>45722.7083333333</v>
       </c>
     </row>
     <row r="326">
@@ -39240,7 +39240,7 @@
         <v>45715</v>
       </c>
       <c r="F327" t="n">
-        <v>45715.58333333334</v>
+        <v>45715.5833333333</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
         <v>10</v>
       </c>
       <c r="L327" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M327" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>45722.58333333334</v>
+        <v>45722.5833333333</v>
       </c>
     </row>
     <row r="328">
@@ -39315,7 +39315,7 @@
         <v>45706</v>
       </c>
       <c r="F328" t="n">
-        <v>45706.58333333334</v>
+        <v>45706.5833333333</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>650</v>
       </c>
       <c r="L328" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M328" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>45721.58333333334</v>
+        <v>45721.5833333333</v>
       </c>
     </row>
     <row r="329">
@@ -39840,7 +39840,7 @@
         <v>45721</v>
       </c>
       <c r="F335" t="n">
-        <v>45721.70833333334</v>
+        <v>45721.7083333333</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>650</v>
       </c>
       <c r="L335" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M335" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>45725.70833333334</v>
+        <v>45725.7083333333</v>
       </c>
     </row>
     <row r="336">
@@ -39915,7 +39915,7 @@
         <v>45713</v>
       </c>
       <c r="F336" t="n">
-        <v>45713.66666666666</v>
+        <v>45713.6666666667</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>650</v>
       </c>
       <c r="L336" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M336" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>45731.66666666666</v>
+        <v>45731.6666666667</v>
       </c>
     </row>
     <row r="337">
@@ -40140,7 +40140,7 @@
         <v>45716</v>
       </c>
       <c r="F339" t="n">
-        <v>45716.66666666666</v>
+        <v>45716.6666666667</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>500</v>
       </c>
       <c r="L339" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M339" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>45728.66666666666</v>
+        <v>45728.6666666667</v>
       </c>
     </row>
     <row r="340">
@@ -40215,7 +40215,7 @@
         <v>45690</v>
       </c>
       <c r="F340" t="n">
-        <v>45690.54166666666</v>
+        <v>45690.5416666667</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>10</v>
       </c>
       <c r="L340" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M340" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>45706.54166666666</v>
+        <v>45706.5416666667</v>
       </c>
     </row>
     <row r="341">
@@ -40290,7 +40290,7 @@
         <v>45713</v>
       </c>
       <c r="F341" t="n">
-        <v>45713.79166666666</v>
+        <v>45713.7916666667</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -40316,7 +40316,7 @@
         <v>650</v>
       </c>
       <c r="L341" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M341" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>45730.79166666666</v>
+        <v>45730.7916666667</v>
       </c>
     </row>
     <row r="342">
@@ -40515,7 +40515,7 @@
         <v>45711</v>
       </c>
       <c r="F344" t="n">
-        <v>45711.79166666666</v>
+        <v>45711.7916666667</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>250</v>
       </c>
       <c r="L344" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M344" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>45721.79166666666</v>
+        <v>45721.7916666667</v>
       </c>
     </row>
     <row r="345">
@@ -40590,7 +40590,7 @@
         <v>45692</v>
       </c>
       <c r="F345" t="n">
-        <v>45692.66666666666</v>
+        <v>45692.6666666667</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>500</v>
       </c>
       <c r="L345" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M345" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>45698.66666666666</v>
+        <v>45698.6666666667</v>
       </c>
     </row>
     <row r="346">
@@ -40665,7 +40665,7 @@
         <v>45692</v>
       </c>
       <c r="F346" t="n">
-        <v>45692.45833333334</v>
+        <v>45692.4583333333</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>500</v>
       </c>
       <c r="L346" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M346" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>45698.45833333334</v>
+        <v>45698.4583333333</v>
       </c>
     </row>
     <row r="347">
@@ -40815,7 +40815,7 @@
         <v>45690</v>
       </c>
       <c r="F348" t="n">
-        <v>45690.54166666666</v>
+        <v>45690.5416666667</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>500</v>
       </c>
       <c r="L348" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M348" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>45704.54166666666</v>
+        <v>45704.5416666667</v>
       </c>
     </row>
     <row r="349">
@@ -41040,7 +41040,7 @@
         <v>45722</v>
       </c>
       <c r="F351" t="n">
-        <v>45722.41666666666</v>
+        <v>45722.4166666667</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>500</v>
       </c>
       <c r="L351" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M351" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>45739.41666666666</v>
+        <v>45739.4166666667</v>
       </c>
     </row>
     <row r="352">
@@ -41115,7 +41115,7 @@
         <v>45707</v>
       </c>
       <c r="F352" t="n">
-        <v>45707.79166666666</v>
+        <v>45707.7916666667</v>
       </c>
       <c r="G352" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>650</v>
       </c>
       <c r="L352" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M352" t="inlineStr">
         <is>
@@ -41164,7 +41164,7 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>45712.79166666666</v>
+        <v>45712.7916666667</v>
       </c>
     </row>
     <row r="353">
@@ -41190,7 +41190,7 @@
         <v>45727</v>
       </c>
       <c r="F353" t="n">
-        <v>45727.58333333334</v>
+        <v>45727.5833333333</v>
       </c>
       <c r="G353" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>500</v>
       </c>
       <c r="L353" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M353" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>45732.58333333334</v>
+        <v>45732.5833333333</v>
       </c>
     </row>
     <row r="354">
@@ -41265,7 +41265,7 @@
         <v>45716</v>
       </c>
       <c r="F354" t="n">
-        <v>45716.41666666666</v>
+        <v>45716.4166666667</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>500</v>
       </c>
       <c r="L354" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M354" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>45732.41666666666</v>
+        <v>45732.4166666667</v>
       </c>
     </row>
     <row r="355">
@@ -41340,7 +41340,7 @@
         <v>45722</v>
       </c>
       <c r="F355" t="n">
-        <v>45722.41666666666</v>
+        <v>45722.4166666667</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>650</v>
       </c>
       <c r="L355" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M355" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>45725.41666666666</v>
+        <v>45725.4166666667</v>
       </c>
     </row>
     <row r="356">
@@ -41490,7 +41490,7 @@
         <v>45696</v>
       </c>
       <c r="F357" t="n">
-        <v>45696.45833333334</v>
+        <v>45696.4583333333</v>
       </c>
       <c r="G357" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>400</v>
       </c>
       <c r="L357" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M357" t="inlineStr">
         <is>
@@ -41539,7 +41539,7 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>45703.45833333334</v>
+        <v>45703.4583333333</v>
       </c>
     </row>
     <row r="358">
@@ -41565,7 +41565,7 @@
         <v>45699</v>
       </c>
       <c r="F358" t="n">
-        <v>45699.45833333334</v>
+        <v>45699.4583333333</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>500</v>
       </c>
       <c r="L358" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M358" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>45713.45833333334</v>
+        <v>45713.4583333333</v>
       </c>
     </row>
     <row r="359">
@@ -41715,7 +41715,7 @@
         <v>45702</v>
       </c>
       <c r="F360" t="n">
-        <v>45702.41666666666</v>
+        <v>45702.4166666667</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>500</v>
       </c>
       <c r="L360" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M360" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>45714.41666666666</v>
+        <v>45714.4166666667</v>
       </c>
     </row>
     <row r="361">
@@ -41940,7 +41940,7 @@
         <v>45725</v>
       </c>
       <c r="F363" t="n">
-        <v>45725.83333333334</v>
+        <v>45725.8333333333</v>
       </c>
       <c r="G363" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>1000</v>
       </c>
       <c r="L363" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M363" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>45739.83333333334</v>
+        <v>45739.8333333333</v>
       </c>
     </row>
     <row r="364">
@@ -42015,7 +42015,7 @@
         <v>45692</v>
       </c>
       <c r="F364" t="n">
-        <v>45692.58333333334</v>
+        <v>45692.5833333333</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>500</v>
       </c>
       <c r="L364" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M364" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>45700.58333333334</v>
+        <v>45700.5833333333</v>
       </c>
     </row>
     <row r="365">
@@ -42090,7 +42090,7 @@
         <v>45712</v>
       </c>
       <c r="F365" t="n">
-        <v>45712.79166666666</v>
+        <v>45712.7916666667</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>650</v>
       </c>
       <c r="L365" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M365" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>45724.79166666666</v>
+        <v>45724.7916666667</v>
       </c>
     </row>
     <row r="366">
@@ -42240,7 +42240,7 @@
         <v>45694</v>
       </c>
       <c r="F367" t="n">
-        <v>45694.41666666666</v>
+        <v>45694.4166666667</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
@@ -42266,7 +42266,7 @@
         <v>250</v>
       </c>
       <c r="L367" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M367" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>45702.41666666666</v>
+        <v>45702.4166666667</v>
       </c>
     </row>
     <row r="368">
@@ -42390,7 +42390,7 @@
         <v>45719</v>
       </c>
       <c r="F369" t="n">
-        <v>45719.79166666666</v>
+        <v>45719.7916666667</v>
       </c>
       <c r="G369" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>250</v>
       </c>
       <c r="L369" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M369" t="inlineStr">
         <is>
@@ -42439,7 +42439,7 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>45734.79166666666</v>
+        <v>45734.7916666667</v>
       </c>
     </row>
     <row r="370">
@@ -42465,7 +42465,7 @@
         <v>45694</v>
       </c>
       <c r="F370" t="n">
-        <v>45694.45833333334</v>
+        <v>45694.4583333333</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>400</v>
       </c>
       <c r="L370" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M370" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>45701.45833333334</v>
+        <v>45701.4583333333</v>
       </c>
     </row>
     <row r="371">
@@ -42540,7 +42540,7 @@
         <v>45727</v>
       </c>
       <c r="F371" t="n">
-        <v>45727.45833333334</v>
+        <v>45727.4583333333</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>400</v>
       </c>
       <c r="L371" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M371" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>45733.45833333334</v>
+        <v>45733.4583333333</v>
       </c>
     </row>
     <row r="372">
@@ -42765,7 +42765,7 @@
         <v>45708</v>
       </c>
       <c r="F374" t="n">
-        <v>45708.58333333334</v>
+        <v>45708.5833333333</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>650</v>
       </c>
       <c r="L374" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M374" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>45712.58333333334</v>
+        <v>45712.5833333333</v>
       </c>
     </row>
     <row r="375">
@@ -42915,7 +42915,7 @@
         <v>45718</v>
       </c>
       <c r="F376" t="n">
-        <v>45718.83333333334</v>
+        <v>45718.8333333333</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>10</v>
       </c>
       <c r="L376" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M376" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>45732.83333333334</v>
+        <v>45732.8333333333</v>
       </c>
     </row>
     <row r="377">
@@ -42990,7 +42990,7 @@
         <v>45724</v>
       </c>
       <c r="F377" t="n">
-        <v>45724.66666666666</v>
+        <v>45724.6666666667</v>
       </c>
       <c r="G377" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>10</v>
       </c>
       <c r="L377" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M377" t="inlineStr">
         <is>
@@ -43039,7 +43039,7 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>45738.66666666666</v>
+        <v>45738.6666666667</v>
       </c>
     </row>
     <row r="378">
@@ -43065,7 +43065,7 @@
         <v>45720</v>
       </c>
       <c r="F378" t="n">
-        <v>45720.79166666666</v>
+        <v>45720.7916666667</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>500</v>
       </c>
       <c r="L378" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M378" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>45724.79166666666</v>
+        <v>45724.7916666667</v>
       </c>
     </row>
     <row r="379">
@@ -43215,7 +43215,7 @@
         <v>45698</v>
       </c>
       <c r="F380" t="n">
-        <v>45698.70833333334</v>
+        <v>45698.7083333333</v>
       </c>
       <c r="G380" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>250</v>
       </c>
       <c r="L380" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M380" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>45704.70833333334</v>
+        <v>45704.7083333333</v>
       </c>
     </row>
     <row r="381">
@@ -43290,7 +43290,7 @@
         <v>45717</v>
       </c>
       <c r="F381" t="n">
-        <v>45717.66666666666</v>
+        <v>45717.6666666667</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>500</v>
       </c>
       <c r="L381" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M381" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>45731.66666666666</v>
+        <v>45731.6666666667</v>
       </c>
     </row>
     <row r="382">
@@ -43440,7 +43440,7 @@
         <v>45698</v>
       </c>
       <c r="F383" t="n">
-        <v>45698.45833333334</v>
+        <v>45698.4583333333</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>250</v>
       </c>
       <c r="L383" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M383" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>45704.45833333334</v>
+        <v>45704.4583333333</v>
       </c>
     </row>
     <row r="384">
@@ -43515,7 +43515,7 @@
         <v>45705</v>
       </c>
       <c r="F384" t="n">
-        <v>45705.66666666666</v>
+        <v>45705.6666666667</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>500</v>
       </c>
       <c r="L384" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M384" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>45713.66666666666</v>
+        <v>45713.6666666667</v>
       </c>
     </row>
     <row r="385">
@@ -43815,7 +43815,7 @@
         <v>45722</v>
       </c>
       <c r="F388" t="n">
-        <v>45722.79166666666</v>
+        <v>45722.7916666667</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>500</v>
       </c>
       <c r="L388" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M388" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>45742.79166666666</v>
+        <v>45742.7916666667</v>
       </c>
     </row>
     <row r="389">
@@ -43965,7 +43965,7 @@
         <v>45699</v>
       </c>
       <c r="F390" t="n">
-        <v>45699.45833333334</v>
+        <v>45699.4583333333</v>
       </c>
       <c r="G390" t="inlineStr">
         <is>
@@ -43991,7 +43991,7 @@
         <v>1000</v>
       </c>
       <c r="L390" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M390" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>45713.45833333334</v>
+        <v>45713.4583333333</v>
       </c>
     </row>
     <row r="391">
@@ -44040,7 +44040,7 @@
         <v>45689</v>
       </c>
       <c r="F391" t="n">
-        <v>45689.83333333334</v>
+        <v>45689.8333333333</v>
       </c>
       <c r="G391" t="inlineStr">
         <is>
@@ -44066,7 +44066,7 @@
         <v>400</v>
       </c>
       <c r="L391" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M391" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         </is>
       </c>
       <c r="Q391" t="n">
-        <v>45698.83333333334</v>
+        <v>45698.8333333333</v>
       </c>
     </row>
     <row r="392">
@@ -44115,7 +44115,7 @@
         <v>45719</v>
       </c>
       <c r="F392" t="n">
-        <v>45719.70833333334</v>
+        <v>45719.7083333333</v>
       </c>
       <c r="G392" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>250</v>
       </c>
       <c r="L392" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M392" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>45732.70833333334</v>
+        <v>45732.7083333333</v>
       </c>
     </row>
     <row r="393">
@@ -44190,7 +44190,7 @@
         <v>45714</v>
       </c>
       <c r="F393" t="n">
-        <v>45714.79166666666</v>
+        <v>45714.7916666667</v>
       </c>
       <c r="G393" t="inlineStr">
         <is>
@@ -44216,7 +44216,7 @@
         <v>400</v>
       </c>
       <c r="L393" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M393" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>45726.79166666666</v>
+        <v>45726.7916666667</v>
       </c>
     </row>
     <row r="394">
@@ -44340,7 +44340,7 @@
         <v>45704</v>
       </c>
       <c r="F395" t="n">
-        <v>45704.58333333334</v>
+        <v>45704.5833333333</v>
       </c>
       <c r="G395" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>500</v>
       </c>
       <c r="L395" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M395" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>45712.58333333334</v>
+        <v>45712.5833333333</v>
       </c>
     </row>
     <row r="396">
@@ -44415,7 +44415,7 @@
         <v>45712</v>
       </c>
       <c r="F396" t="n">
-        <v>45712.83333333334</v>
+        <v>45712.8333333333</v>
       </c>
       <c r="G396" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>400</v>
       </c>
       <c r="L396" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M396" t="inlineStr">
         <is>
@@ -44464,7 +44464,7 @@
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>45728.83333333334</v>
+        <v>45728.8333333333</v>
       </c>
     </row>
     <row r="397">
@@ -44490,7 +44490,7 @@
         <v>45701</v>
       </c>
       <c r="F397" t="n">
-        <v>45701.70833333334</v>
+        <v>45701.7083333333</v>
       </c>
       <c r="G397" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         <v>400</v>
       </c>
       <c r="L397" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M397" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>45704.70833333334</v>
+        <v>45704.7083333333</v>
       </c>
     </row>
     <row r="398">
@@ -44565,7 +44565,7 @@
         <v>45689</v>
       </c>
       <c r="F398" t="n">
-        <v>45689.79166666666</v>
+        <v>45689.7916666667</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
@@ -44591,7 +44591,7 @@
         <v>400</v>
       </c>
       <c r="L398" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M398" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>45708.79166666666</v>
+        <v>45708.7916666667</v>
       </c>
     </row>
     <row r="399">
@@ -44640,7 +44640,7 @@
         <v>45720</v>
       </c>
       <c r="F399" t="n">
-        <v>45720.70833333334</v>
+        <v>45720.7083333333</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -44666,7 +44666,7 @@
         <v>10</v>
       </c>
       <c r="L399" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M399" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>45736.70833333334</v>
+        <v>45736.7083333333</v>
       </c>
     </row>
     <row r="400">
@@ -44715,7 +44715,7 @@
         <v>45692</v>
       </c>
       <c r="F400" t="n">
-        <v>45692.83333333334</v>
+        <v>45692.8333333333</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
@@ -44741,7 +44741,7 @@
         <v>10</v>
       </c>
       <c r="L400" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M400" t="inlineStr">
         <is>
@@ -44764,7 +44764,7 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>45697.83333333334</v>
+        <v>45697.8333333333</v>
       </c>
     </row>
     <row r="401">
@@ -44790,7 +44790,7 @@
         <v>45701</v>
       </c>
       <c r="F401" t="n">
-        <v>45701.79166666666</v>
+        <v>45701.7916666667</v>
       </c>
       <c r="G401" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>650</v>
       </c>
       <c r="L401" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M401" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>45705.79166666666</v>
+        <v>45705.7916666667</v>
       </c>
     </row>
     <row r="402">
@@ -44865,7 +44865,7 @@
         <v>45695</v>
       </c>
       <c r="F402" t="n">
-        <v>45695.66666666666</v>
+        <v>45695.6666666667</v>
       </c>
       <c r="G402" t="inlineStr">
         <is>
@@ -44891,7 +44891,7 @@
         <v>650</v>
       </c>
       <c r="L402" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M402" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>45711.66666666666</v>
+        <v>45711.6666666667</v>
       </c>
     </row>
     <row r="403">
@@ -44940,7 +44940,7 @@
         <v>45711</v>
       </c>
       <c r="F403" t="n">
-        <v>45711.45833333334</v>
+        <v>45711.4583333333</v>
       </c>
       <c r="G403" t="inlineStr">
         <is>
@@ -44966,7 +44966,7 @@
         <v>10</v>
       </c>
       <c r="L403" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M403" t="inlineStr">
         <is>
@@ -44989,7 +44989,7 @@
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>45729.45833333334</v>
+        <v>45729.4583333333</v>
       </c>
     </row>
     <row r="404">
@@ -45240,7 +45240,7 @@
         <v>45697</v>
       </c>
       <c r="F407" t="n">
-        <v>45697.66666666666</v>
+        <v>45697.6666666667</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>10</v>
       </c>
       <c r="L407" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M407" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         </is>
       </c>
       <c r="Q407" t="n">
-        <v>45713.66666666666</v>
+        <v>45713.6666666667</v>
       </c>
     </row>
     <row r="408">
@@ -45315,7 +45315,7 @@
         <v>45698</v>
       </c>
       <c r="F408" t="n">
-        <v>45698.58333333334</v>
+        <v>45698.5833333333</v>
       </c>
       <c r="G408" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>1000</v>
       </c>
       <c r="L408" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M408" t="inlineStr">
         <is>
@@ -45364,7 +45364,7 @@
         </is>
       </c>
       <c r="Q408" t="n">
-        <v>45714.58333333334</v>
+        <v>45714.5833333333</v>
       </c>
     </row>
     <row r="409">
@@ -45390,7 +45390,7 @@
         <v>45728</v>
       </c>
       <c r="F409" t="n">
-        <v>45728.83333333334</v>
+        <v>45728.8333333333</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
@@ -45416,7 +45416,7 @@
         <v>250</v>
       </c>
       <c r="L409" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M409" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         </is>
       </c>
       <c r="Q409" t="n">
-        <v>45740.83333333334</v>
+        <v>45740.8333333333</v>
       </c>
     </row>
     <row r="410">
@@ -45615,7 +45615,7 @@
         <v>45720</v>
       </c>
       <c r="F412" t="n">
-        <v>45720.54166666666</v>
+        <v>45720.5416666667</v>
       </c>
       <c r="G412" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>400</v>
       </c>
       <c r="L412" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M412" t="inlineStr">
         <is>
@@ -45664,7 +45664,7 @@
         </is>
       </c>
       <c r="Q412" t="n">
-        <v>45733.54166666666</v>
+        <v>45733.5416666667</v>
       </c>
     </row>
     <row r="413">
@@ -45690,7 +45690,7 @@
         <v>45692</v>
       </c>
       <c r="F413" t="n">
-        <v>45692.83333333334</v>
+        <v>45692.8333333333</v>
       </c>
       <c r="G413" t="inlineStr">
         <is>
@@ -45716,7 +45716,7 @@
         <v>250</v>
       </c>
       <c r="L413" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M413" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         </is>
       </c>
       <c r="Q413" t="n">
-        <v>45711.83333333334</v>
+        <v>45711.8333333333</v>
       </c>
     </row>
     <row r="414">
@@ -45765,7 +45765,7 @@
         <v>45725</v>
       </c>
       <c r="F414" t="n">
-        <v>45725.79166666666</v>
+        <v>45725.7916666667</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>500</v>
       </c>
       <c r="L414" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M414" t="inlineStr">
         <is>
@@ -45814,7 +45814,7 @@
         </is>
       </c>
       <c r="Q414" t="n">
-        <v>45730.79166666666</v>
+        <v>45730.7916666667</v>
       </c>
     </row>
     <row r="415">
@@ -45990,7 +45990,7 @@
         <v>45729</v>
       </c>
       <c r="F417" t="n">
-        <v>45729.54166666666</v>
+        <v>45729.5416666667</v>
       </c>
       <c r="G417" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>500</v>
       </c>
       <c r="L417" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M417" t="inlineStr">
         <is>
@@ -46039,7 +46039,7 @@
         </is>
       </c>
       <c r="Q417" t="n">
-        <v>45748.54166666666</v>
+        <v>45748.5416666667</v>
       </c>
     </row>
     <row r="418">
@@ -46140,7 +46140,7 @@
         <v>45723</v>
       </c>
       <c r="F419" t="n">
-        <v>45723.54166666666</v>
+        <v>45723.5416666667</v>
       </c>
       <c r="G419" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>10</v>
       </c>
       <c r="L419" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M419" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         </is>
       </c>
       <c r="Q419" t="n">
-        <v>45735.54166666666</v>
+        <v>45735.5416666667</v>
       </c>
     </row>
     <row r="420">
@@ -46215,7 +46215,7 @@
         <v>45726</v>
       </c>
       <c r="F420" t="n">
-        <v>45726.41666666666</v>
+        <v>45726.4166666667</v>
       </c>
       <c r="G420" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>650</v>
       </c>
       <c r="L420" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M420" t="inlineStr">
         <is>
@@ -46264,7 +46264,7 @@
         </is>
       </c>
       <c r="Q420" t="n">
-        <v>45729.41666666666</v>
+        <v>45729.4166666667</v>
       </c>
     </row>
     <row r="421">
@@ -46290,7 +46290,7 @@
         <v>45697</v>
       </c>
       <c r="F421" t="n">
-        <v>45697.70833333334</v>
+        <v>45697.7083333333</v>
       </c>
       <c r="G421" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>1000</v>
       </c>
       <c r="L421" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M421" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         </is>
       </c>
       <c r="Q421" t="n">
-        <v>45709.70833333334</v>
+        <v>45709.7083333333</v>
       </c>
     </row>
     <row r="422">
@@ -46440,7 +46440,7 @@
         <v>45728</v>
       </c>
       <c r="F423" t="n">
-        <v>45728.79166666666</v>
+        <v>45728.7916666667</v>
       </c>
       <c r="G423" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>250</v>
       </c>
       <c r="L423" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M423" t="inlineStr">
         <is>
@@ -46489,7 +46489,7 @@
         </is>
       </c>
       <c r="Q423" t="n">
-        <v>45736.79166666666</v>
+        <v>45736.7916666667</v>
       </c>
     </row>
     <row r="424">
@@ -46515,7 +46515,7 @@
         <v>45719</v>
       </c>
       <c r="F424" t="n">
-        <v>45719.83333333334</v>
+        <v>45719.8333333333</v>
       </c>
       <c r="G424" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>500</v>
       </c>
       <c r="L424" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M424" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         </is>
       </c>
       <c r="Q424" t="n">
-        <v>45733.83333333334</v>
+        <v>45733.8333333333</v>
       </c>
     </row>
     <row r="425">
@@ -46590,7 +46590,7 @@
         <v>45717</v>
       </c>
       <c r="F425" t="n">
-        <v>45717.54166666666</v>
+        <v>45717.5416666667</v>
       </c>
       <c r="G425" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>250</v>
       </c>
       <c r="L425" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M425" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         </is>
       </c>
       <c r="Q425" t="n">
-        <v>45732.54166666666</v>
+        <v>45732.5416666667</v>
       </c>
     </row>
     <row r="426">
@@ -46740,7 +46740,7 @@
         <v>45706</v>
       </c>
       <c r="F427" t="n">
-        <v>45706.70833333334</v>
+        <v>45706.7083333333</v>
       </c>
       <c r="G427" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>250</v>
       </c>
       <c r="L427" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M427" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         </is>
       </c>
       <c r="Q427" t="n">
-        <v>45711.70833333334</v>
+        <v>45711.7083333333</v>
       </c>
     </row>
     <row r="428">
@@ -46815,7 +46815,7 @@
         <v>45711</v>
       </c>
       <c r="F428" t="n">
-        <v>45711.58333333334</v>
+        <v>45711.5833333333</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>10</v>
       </c>
       <c r="L428" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M428" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         </is>
       </c>
       <c r="Q428" t="n">
-        <v>45715.58333333334</v>
+        <v>45715.5833333333</v>
       </c>
     </row>
     <row r="429">
@@ -46890,7 +46890,7 @@
         <v>45696</v>
       </c>
       <c r="F429" t="n">
-        <v>45696.79166666666</v>
+        <v>45696.7916666667</v>
       </c>
       <c r="G429" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>250</v>
       </c>
       <c r="L429" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M429" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         </is>
       </c>
       <c r="Q429" t="n">
-        <v>45712.79166666666</v>
+        <v>45712.7916666667</v>
       </c>
     </row>
     <row r="430">
@@ -47115,7 +47115,7 @@
         <v>45727</v>
       </c>
       <c r="F432" t="n">
-        <v>45727.70833333334</v>
+        <v>45727.7083333333</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
@@ -47141,7 +47141,7 @@
         <v>500</v>
       </c>
       <c r="L432" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M432" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         </is>
       </c>
       <c r="Q432" t="n">
-        <v>45746.70833333334</v>
+        <v>45746.7083333333</v>
       </c>
     </row>
     <row r="433">
@@ -47190,7 +47190,7 @@
         <v>45714</v>
       </c>
       <c r="F433" t="n">
-        <v>45714.58333333334</v>
+        <v>45714.5833333333</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
@@ -47216,7 +47216,7 @@
         <v>400</v>
       </c>
       <c r="L433" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M433" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         </is>
       </c>
       <c r="Q433" t="n">
-        <v>45727.58333333334</v>
+        <v>45727.5833333333</v>
       </c>
     </row>
     <row r="434">
@@ -47265,7 +47265,7 @@
         <v>45710</v>
       </c>
       <c r="F434" t="n">
-        <v>45710.58333333334</v>
+        <v>45710.5833333333</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>500</v>
       </c>
       <c r="L434" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M434" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         </is>
       </c>
       <c r="Q434" t="n">
-        <v>45728.58333333334</v>
+        <v>45728.5833333333</v>
       </c>
     </row>
     <row r="435">
@@ -47340,7 +47340,7 @@
         <v>45711</v>
       </c>
       <c r="F435" t="n">
-        <v>45711.54166666666</v>
+        <v>45711.5416666667</v>
       </c>
       <c r="G435" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>1000</v>
       </c>
       <c r="L435" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M435" t="inlineStr">
         <is>
@@ -47389,7 +47389,7 @@
         </is>
       </c>
       <c r="Q435" t="n">
-        <v>45722.54166666666</v>
+        <v>45722.5416666667</v>
       </c>
     </row>
     <row r="436">
@@ -47415,7 +47415,7 @@
         <v>45705</v>
       </c>
       <c r="F436" t="n">
-        <v>45705.70833333334</v>
+        <v>45705.7083333333</v>
       </c>
       <c r="G436" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>650</v>
       </c>
       <c r="L436" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M436" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         </is>
       </c>
       <c r="Q436" t="n">
-        <v>45719.70833333334</v>
+        <v>45719.7083333333</v>
       </c>
     </row>
     <row r="437">
@@ -47790,7 +47790,7 @@
         <v>45713</v>
       </c>
       <c r="F441" t="n">
-        <v>45713.54166666666</v>
+        <v>45713.5416666667</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>
@@ -47816,7 +47816,7 @@
         <v>400</v>
       </c>
       <c r="L441" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M441" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         </is>
       </c>
       <c r="Q441" t="n">
-        <v>45725.54166666666</v>
+        <v>45725.5416666667</v>
       </c>
     </row>
     <row r="442">
@@ -48015,7 +48015,7 @@
         <v>45711</v>
       </c>
       <c r="F444" t="n">
-        <v>45711.66666666666</v>
+        <v>45711.6666666667</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>1000</v>
       </c>
       <c r="L444" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M444" t="inlineStr">
         <is>
@@ -48064,7 +48064,7 @@
         </is>
       </c>
       <c r="Q444" t="n">
-        <v>45729.66666666666</v>
+        <v>45729.6666666667</v>
       </c>
     </row>
     <row r="445">
@@ -48165,7 +48165,7 @@
         <v>45724</v>
       </c>
       <c r="F446" t="n">
-        <v>45724.70833333334</v>
+        <v>45724.7083333333</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>650</v>
       </c>
       <c r="L446" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M446" t="inlineStr">
         <is>
@@ -48214,7 +48214,7 @@
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>45742.70833333334</v>
+        <v>45742.7083333333</v>
       </c>
     </row>
     <row r="447">
@@ -48315,7 +48315,7 @@
         <v>45724</v>
       </c>
       <c r="F448" t="n">
-        <v>45724.79166666666</v>
+        <v>45724.7916666667</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -48341,7 +48341,7 @@
         <v>1000</v>
       </c>
       <c r="L448" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M448" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         </is>
       </c>
       <c r="Q448" t="n">
-        <v>45738.79166666666</v>
+        <v>45738.7916666667</v>
       </c>
     </row>
     <row r="449">
@@ -48390,7 +48390,7 @@
         <v>45692</v>
       </c>
       <c r="F449" t="n">
-        <v>45692.41666666666</v>
+        <v>45692.4166666667</v>
       </c>
       <c r="G449" t="inlineStr">
         <is>
@@ -48416,7 +48416,7 @@
         <v>650</v>
       </c>
       <c r="L449" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M449" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         </is>
       </c>
       <c r="Q449" t="n">
-        <v>45709.41666666666</v>
+        <v>45709.4166666667</v>
       </c>
     </row>
     <row r="450">
@@ -48465,7 +48465,7 @@
         <v>45729</v>
       </c>
       <c r="F450" t="n">
-        <v>45729.79166666666</v>
+        <v>45729.7916666667</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>400</v>
       </c>
       <c r="L450" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M450" t="inlineStr">
         <is>
@@ -48514,7 +48514,7 @@
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>45743.79166666666</v>
+        <v>45743.7916666667</v>
       </c>
     </row>
     <row r="451">
@@ -48540,7 +48540,7 @@
         <v>45690</v>
       </c>
       <c r="F451" t="n">
-        <v>45690.58333333334</v>
+        <v>45690.5833333333</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>500</v>
       </c>
       <c r="L451" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M451" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         </is>
       </c>
       <c r="Q451" t="n">
-        <v>45693.58333333334</v>
+        <v>45693.5833333333</v>
       </c>
     </row>
     <row r="452">
@@ -48765,7 +48765,7 @@
         <v>45718</v>
       </c>
       <c r="F454" t="n">
-        <v>45718.58333333334</v>
+        <v>45718.5833333333</v>
       </c>
       <c r="G454" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>400</v>
       </c>
       <c r="L454" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M454" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         </is>
       </c>
       <c r="Q454" t="n">
-        <v>45727.58333333334</v>
+        <v>45727.5833333333</v>
       </c>
     </row>
     <row r="455">
@@ -48840,7 +48840,7 @@
         <v>45716</v>
       </c>
       <c r="F455" t="n">
-        <v>45716.54166666666</v>
+        <v>45716.5416666667</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>650</v>
       </c>
       <c r="L455" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M455" t="inlineStr">
         <is>
@@ -48889,7 +48889,7 @@
         </is>
       </c>
       <c r="Q455" t="n">
-        <v>45736.54166666666</v>
+        <v>45736.5416666667</v>
       </c>
     </row>
     <row r="456">
@@ -48990,7 +48990,7 @@
         <v>45719</v>
       </c>
       <c r="F457" t="n">
-        <v>45719.41666666666</v>
+        <v>45719.4166666667</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
@@ -49016,7 +49016,7 @@
         <v>650</v>
       </c>
       <c r="L457" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M457" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         </is>
       </c>
       <c r="Q457" t="n">
-        <v>45737.41666666666</v>
+        <v>45737.4166666667</v>
       </c>
     </row>
     <row r="458">
@@ -49065,7 +49065,7 @@
         <v>45723</v>
       </c>
       <c r="F458" t="n">
-        <v>45723.83333333334</v>
+        <v>45723.8333333333</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         <v>10</v>
       </c>
       <c r="L458" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M458" t="inlineStr">
         <is>
@@ -49114,7 +49114,7 @@
         </is>
       </c>
       <c r="Q458" t="n">
-        <v>45741.83333333334</v>
+        <v>45741.8333333333</v>
       </c>
     </row>
     <row r="459">
@@ -49140,7 +49140,7 @@
         <v>45725</v>
       </c>
       <c r="F459" t="n">
-        <v>45725.83333333334</v>
+        <v>45725.8333333333</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>10</v>
       </c>
       <c r="L459" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M459" t="inlineStr">
         <is>
@@ -49189,7 +49189,7 @@
         </is>
       </c>
       <c r="Q459" t="n">
-        <v>45728.83333333334</v>
+        <v>45728.8333333333</v>
       </c>
     </row>
     <row r="460">
@@ -49290,7 +49290,7 @@
         <v>45727</v>
       </c>
       <c r="F461" t="n">
-        <v>45727.41666666666</v>
+        <v>45727.4166666667</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -49316,7 +49316,7 @@
         <v>500</v>
       </c>
       <c r="L461" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M461" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         </is>
       </c>
       <c r="Q461" t="n">
-        <v>45731.41666666666</v>
+        <v>45731.4166666667</v>
       </c>
     </row>
     <row r="462">
@@ -49815,7 +49815,7 @@
         <v>45694</v>
       </c>
       <c r="F468" t="n">
-        <v>45694.41666666666</v>
+        <v>45694.4166666667</v>
       </c>
       <c r="G468" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>650</v>
       </c>
       <c r="L468" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M468" t="inlineStr">
         <is>
@@ -49864,7 +49864,7 @@
         </is>
       </c>
       <c r="Q468" t="n">
-        <v>45699.41666666666</v>
+        <v>45699.4166666667</v>
       </c>
     </row>
     <row r="469">
@@ -49890,7 +49890,7 @@
         <v>45710</v>
       </c>
       <c r="F469" t="n">
-        <v>45710.70833333334</v>
+        <v>45710.7083333333</v>
       </c>
       <c r="G469" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>250</v>
       </c>
       <c r="L469" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M469" t="inlineStr">
         <is>
@@ -49939,7 +49939,7 @@
         </is>
       </c>
       <c r="Q469" t="n">
-        <v>45725.70833333334</v>
+        <v>45725.7083333333</v>
       </c>
     </row>
     <row r="470">
@@ -49965,7 +49965,7 @@
         <v>45729</v>
       </c>
       <c r="F470" t="n">
-        <v>45729.70833333334</v>
+        <v>45729.7083333333</v>
       </c>
       <c r="G470" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>650</v>
       </c>
       <c r="L470" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7083333333</v>
       </c>
       <c r="M470" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         </is>
       </c>
       <c r="Q470" t="n">
-        <v>45736.70833333334</v>
+        <v>45736.7083333333</v>
       </c>
     </row>
     <row r="471">
@@ -50040,7 +50040,7 @@
         <v>45711</v>
       </c>
       <c r="F471" t="n">
-        <v>45711.45833333334</v>
+        <v>45711.4583333333</v>
       </c>
       <c r="G471" t="inlineStr">
         <is>
@@ -50066,7 +50066,7 @@
         <v>10</v>
       </c>
       <c r="L471" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M471" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         </is>
       </c>
       <c r="Q471" t="n">
-        <v>45717.45833333334</v>
+        <v>45717.4583333333</v>
       </c>
     </row>
     <row r="472">
@@ -50115,7 +50115,7 @@
         <v>45718</v>
       </c>
       <c r="F472" t="n">
-        <v>45718.83333333334</v>
+        <v>45718.8333333333</v>
       </c>
       <c r="G472" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>400</v>
       </c>
       <c r="L472" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M472" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         </is>
       </c>
       <c r="Q472" t="n">
-        <v>45723.83333333334</v>
+        <v>45723.8333333333</v>
       </c>
     </row>
     <row r="473">
@@ -50340,7 +50340,7 @@
         <v>45705</v>
       </c>
       <c r="F475" t="n">
-        <v>45705.54166666666</v>
+        <v>45705.5416666667</v>
       </c>
       <c r="G475" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>400</v>
       </c>
       <c r="L475" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M475" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         </is>
       </c>
       <c r="Q475" t="n">
-        <v>45722.54166666666</v>
+        <v>45722.5416666667</v>
       </c>
     </row>
     <row r="476">
@@ -50640,7 +50640,7 @@
         <v>45721</v>
       </c>
       <c r="F479" t="n">
-        <v>45721.41666666666</v>
+        <v>45721.4166666667</v>
       </c>
       <c r="G479" t="inlineStr">
         <is>
@@ -50666,7 +50666,7 @@
         <v>10</v>
       </c>
       <c r="L479" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M479" t="inlineStr">
         <is>
@@ -50689,7 +50689,7 @@
         </is>
       </c>
       <c r="Q479" t="n">
-        <v>45733.41666666666</v>
+        <v>45733.4166666667</v>
       </c>
     </row>
     <row r="480">
@@ -50715,7 +50715,7 @@
         <v>45689</v>
       </c>
       <c r="F480" t="n">
-        <v>45689.54166666666</v>
+        <v>45689.5416666667</v>
       </c>
       <c r="G480" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         <v>500</v>
       </c>
       <c r="L480" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M480" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         </is>
       </c>
       <c r="Q480" t="n">
-        <v>45701.54166666666</v>
+        <v>45701.5416666667</v>
       </c>
     </row>
     <row r="481">
@@ -50790,7 +50790,7 @@
         <v>45728</v>
       </c>
       <c r="F481" t="n">
-        <v>45728.83333333334</v>
+        <v>45728.8333333333</v>
       </c>
       <c r="G481" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>500</v>
       </c>
       <c r="L481" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8333333333</v>
       </c>
       <c r="M481" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         </is>
       </c>
       <c r="Q481" t="n">
-        <v>45744.83333333334</v>
+        <v>45744.8333333333</v>
       </c>
     </row>
     <row r="482">
@@ -50940,7 +50940,7 @@
         <v>45702</v>
       </c>
       <c r="F483" t="n">
-        <v>45702.58333333334</v>
+        <v>45702.5833333333</v>
       </c>
       <c r="G483" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>250</v>
       </c>
       <c r="L483" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M483" t="inlineStr">
         <is>
@@ -50989,7 +50989,7 @@
         </is>
       </c>
       <c r="Q483" t="n">
-        <v>45709.58333333334</v>
+        <v>45709.5833333333</v>
       </c>
     </row>
     <row r="484">
@@ -51015,7 +51015,7 @@
         <v>45690</v>
       </c>
       <c r="F484" t="n">
-        <v>45690.54166666666</v>
+        <v>45690.5416666667</v>
       </c>
       <c r="G484" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>500</v>
       </c>
       <c r="L484" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5416666667</v>
       </c>
       <c r="M484" t="inlineStr">
         <is>
@@ -51064,7 +51064,7 @@
         </is>
       </c>
       <c r="Q484" t="n">
-        <v>45697.54166666666</v>
+        <v>45697.5416666667</v>
       </c>
     </row>
     <row r="485">
@@ -51240,7 +51240,7 @@
         <v>45701</v>
       </c>
       <c r="F487" t="n">
-        <v>45701.41666666666</v>
+        <v>45701.4166666667</v>
       </c>
       <c r="G487" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
         <v>500</v>
       </c>
       <c r="L487" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M487" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         </is>
       </c>
       <c r="Q487" t="n">
-        <v>45716.41666666666</v>
+        <v>45716.4166666667</v>
       </c>
     </row>
     <row r="488">
@@ -51315,7 +51315,7 @@
         <v>45706</v>
       </c>
       <c r="F488" t="n">
-        <v>45706.45833333334</v>
+        <v>45706.4583333333</v>
       </c>
       <c r="G488" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>650</v>
       </c>
       <c r="L488" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M488" t="inlineStr">
         <is>
@@ -51364,7 +51364,7 @@
         </is>
       </c>
       <c r="Q488" t="n">
-        <v>45722.45833333334</v>
+        <v>45722.4583333333</v>
       </c>
     </row>
     <row r="489">
@@ -51690,7 +51690,7 @@
         <v>45720</v>
       </c>
       <c r="F493" t="n">
-        <v>45720.66666666666</v>
+        <v>45720.6666666667</v>
       </c>
       <c r="G493" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>500</v>
       </c>
       <c r="L493" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6666666667000001</v>
       </c>
       <c r="M493" t="inlineStr">
         <is>
@@ -51739,7 +51739,7 @@
         </is>
       </c>
       <c r="Q493" t="n">
-        <v>45735.66666666666</v>
+        <v>45735.6666666667</v>
       </c>
     </row>
     <row r="494">
@@ -51765,7 +51765,7 @@
         <v>45696</v>
       </c>
       <c r="F494" t="n">
-        <v>45696.41666666666</v>
+        <v>45696.4166666667</v>
       </c>
       <c r="G494" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>650</v>
       </c>
       <c r="L494" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4166666667</v>
       </c>
       <c r="M494" t="inlineStr">
         <is>
@@ -51814,7 +51814,7 @@
         </is>
       </c>
       <c r="Q494" t="n">
-        <v>45701.41666666666</v>
+        <v>45701.4166666667</v>
       </c>
     </row>
     <row r="495">
@@ -51990,7 +51990,7 @@
         <v>45691</v>
       </c>
       <c r="F497" t="n">
-        <v>45691.58333333334</v>
+        <v>45691.5833333333</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>
@@ -52016,7 +52016,7 @@
         <v>500</v>
       </c>
       <c r="L497" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5833333333</v>
       </c>
       <c r="M497" t="inlineStr">
         <is>
@@ -52039,7 +52039,7 @@
         </is>
       </c>
       <c r="Q497" t="n">
-        <v>45699.58333333334</v>
+        <v>45699.5833333333</v>
       </c>
     </row>
     <row r="498">
@@ -52140,7 +52140,7 @@
         <v>45690</v>
       </c>
       <c r="F499" t="n">
-        <v>45690.45833333334</v>
+        <v>45690.4583333333</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>650</v>
       </c>
       <c r="L499" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M499" t="inlineStr">
         <is>
@@ -52189,7 +52189,7 @@
         </is>
       </c>
       <c r="Q499" t="n">
-        <v>45701.45833333334</v>
+        <v>45701.4583333333</v>
       </c>
     </row>
     <row r="500">
@@ -52215,7 +52215,7 @@
         <v>45725</v>
       </c>
       <c r="F500" t="n">
-        <v>45725.45833333334</v>
+        <v>45725.4583333333</v>
       </c>
       <c r="G500" t="inlineStr">
         <is>
@@ -52241,7 +52241,7 @@
         <v>400</v>
       </c>
       <c r="L500" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4583333333</v>
       </c>
       <c r="M500" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         </is>
       </c>
       <c r="Q500" t="n">
-        <v>45734.45833333334</v>
+        <v>45734.4583333333</v>
       </c>
     </row>
     <row r="501">
@@ -52290,7 +52290,7 @@
         <v>45708</v>
       </c>
       <c r="F501" t="n">
-        <v>45708.79166666666</v>
+        <v>45708.7916666667</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>1000</v>
       </c>
       <c r="L501" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7916666667000001</v>
       </c>
       <c r="M501" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
         </is>
       </c>
       <c r="Q501" t="n">
-        <v>45727.79166666666</v>
+        <v>45727.7916666667</v>
       </c>
     </row>
   </sheetData>
@@ -52894,7 +52894,7 @@
         <v>102</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>46.93</v>
